--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -2140,7 +2140,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="B8" s="5">
         <f>IF(A8="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A8,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2149,10 +2153,20 @@
         <f>IF(A8="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A8,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5">
         <f>IF(E8="","",IF(AND(F8="نعم",G8="نعم"),"جرد + مراجعة",IF(F8="نعم","جرد فقط",IF(G8="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2163,7 +2177,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="B9" s="5">
         <f>IF(A9="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A9,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2172,10 +2190,20 @@
         <f>IF(A9="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A9,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="D9" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5">
         <f>IF(E9="","",IF(AND(F9="نعم",G9="نعم"),"جرد + مراجعة",IF(F9="نعم","جرد فقط",IF(G9="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -2166,7 +2166,11 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H8" s="5">
         <f>IF(E8="","",IF(AND(F8="نعم",G8="نعم"),"جرد + مراجعة",IF(F8="نعم","جرد فقط",IF(G8="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2191,65 +2195,97 @@
         <v/>
       </c>
       <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(E9="","",IF(AND(F9="نعم",G9="نعم"),"جرد + مراجعة",IF(F9="نعم","جرد فقط",IF(G9="نعم","مراجعة فقط",""))))</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>IF(H9="جرد + مراجعة",الإعدادات!$B$2,IF(H9="مراجعة فقط",الإعدادات!$B$3,IF(H9="جرد فقط",الإعدادات!$B$4,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>IF(A10="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A10,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>IF(A10="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A10,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H10" s="5">
+        <f>IF(E10="","",IF(AND(F10="نعم",G10="نعم"),"جرد + مراجعة",IF(F10="نعم","جرد فقط",IF(G10="نعم","مراجعة فقط",""))))</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>IF(H10="جرد + مراجعة",الإعدادات!$B$2,IF(H10="مراجعة فقط",الإعدادات!$B$3,IF(H10="جرد فقط",الإعدادات!$B$4,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>IF(A11="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A11,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>IF(A11="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A11,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>د. علي خليفة</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5">
-        <f>IF(E9="","",IF(AND(F9="نعم",G9="نعم"),"جرد + مراجعة",IF(F9="نعم","جرد فقط",IF(G9="نعم","مراجعة فقط",""))))</f>
-        <v/>
-      </c>
-      <c r="I9" s="9">
-        <f>IF(H9="جرد + مراجعة",الإعدادات!$B$2,IF(H9="مراجعة فقط",الإعدادات!$B$3,IF(H9="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="5">
-        <f>IF(A10="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A10,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C10" s="5">
-        <f>IF(A10="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A10,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="5">
-        <f>IF(E10="","",IF(AND(F10="نعم",G10="نعم"),"جرد + مراجعة",IF(F10="نعم","جرد فقط",IF(G10="نعم","مراجعة فقط",""))))</f>
-        <v/>
-      </c>
-      <c r="I10" s="9">
-        <f>IF(H10="جرد + مراجعة",الإعدادات!$B$2,IF(H10="مراجعة فقط",الإعدادات!$B$3,IF(H10="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="5">
-        <f>IF(A11="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A11,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C11" s="5">
-        <f>IF(A11="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A11,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H11" s="5">
         <f>IF(E11="","",IF(AND(F11="نعم",G11="نعم"),"جرد + مراجعة",IF(F11="نعم","جرد فقط",IF(G11="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2260,7 +2296,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="B12" s="5">
         <f>IF(A12="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A12,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2269,10 +2309,20 @@
         <f>IF(A12="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A12,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="D12" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H12" s="5">
         <f>IF(E12="","",IF(AND(F12="نعم",G12="نعم"),"جرد + مراجعة",IF(F12="نعم","جرد فقط",IF(G12="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2283,7 +2333,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="B13" s="5">
         <f>IF(A13="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A13,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2292,10 +2346,20 @@
         <f>IF(A13="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A13,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="D13" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H13" s="5">
         <f>IF(E13="","",IF(AND(F13="نعم",G13="نعم"),"جرد + مراجعة",IF(F13="نعم","جرد فقط",IF(G13="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -658,7 +658,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
       <c r="B7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
         <v/>
@@ -2370,7 +2374,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="B14" s="5">
         <f>IF(A14="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A14,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2379,10 +2387,20 @@
         <f>IF(A14="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A14,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="D14" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H14" s="5">
         <f>IF(E14="","",IF(AND(F14="نعم",G14="نعم"),"جرد + مراجعة",IF(F14="نعم","جرد فقط",IF(G14="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2393,7 +2411,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="B15" s="5">
         <f>IF(A15="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A15,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2402,10 +2424,20 @@
         <f>IF(A15="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A15,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="D15" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="5">
         <f>IF(E15="","",IF(AND(F15="نعم",G15="نعم"),"جرد + مراجعة",IF(F15="نعم","جرد فقط",IF(G15="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2416,7 +2448,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="B16" s="5">
         <f>IF(A16="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A16,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2425,10 +2461,20 @@
         <f>IF(A16="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A16,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="D16" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5">
         <f>IF(E16="","",IF(AND(F16="نعم",G16="نعم"),"جرد + مراجعة",IF(F16="نعم","جرد فقط",IF(G16="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -2437,7 +2437,11 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H15" s="5">
         <f>IF(E15="","",IF(AND(F15="نعم",G15="نعم"),"جرد + مراجعة",IF(F15="نعم","جرد فقط",IF(G15="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2462,88 +2466,134 @@
         <v/>
       </c>
       <c r="D16" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(E16="","",IF(AND(F16="نعم",G16="نعم"),"جرد + مراجعة",IF(F16="نعم","جرد فقط",IF(G16="نعم","مراجعة فقط",""))))</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>IF(H16="جرد + مراجعة",الإعدادات!$B$2,IF(H16="مراجعة فقط",الإعدادات!$B$3,IF(H16="جرد فقط",الإعدادات!$B$4,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>IF(A17="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A17,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C17" s="5">
+        <f>IF(A17="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A17,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(E17="","",IF(AND(F17="نعم",G17="نعم"),"جرد + مراجعة",IF(F17="نعم","جرد فقط",IF(G17="نعم","مراجعة فقط",""))))</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>IF(H17="جرد + مراجعة",الإعدادات!$B$2,IF(H17="مراجعة فقط",الإعدادات!$B$3,IF(H17="جرد فقط",الإعدادات!$B$4,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>IF(A18="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A18,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C18" s="5">
+        <f>IF(A18="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A18,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(E18="","",IF(AND(F18="نعم",G18="نعم"),"جرد + مراجعة",IF(F18="نعم","جرد فقط",IF(G18="نعم","مراجعة فقط",""))))</f>
+        <v/>
+      </c>
+      <c r="I18" s="9">
+        <f>IF(H18="جرد + مراجعة",الإعدادات!$B$2,IF(H18="مراجعة فقط",الإعدادات!$B$3,IF(H18="جرد فقط",الإعدادات!$B$4,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>IF(A19="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A19,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C19" s="5">
+        <f>IF(A19="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A19,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>د. حسام شلش</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="5">
-        <f>IF(E16="","",IF(AND(F16="نعم",G16="نعم"),"جرد + مراجعة",IF(F16="نعم","جرد فقط",IF(G16="نعم","مراجعة فقط",""))))</f>
-        <v/>
-      </c>
-      <c r="I16" s="9">
-        <f>IF(H16="جرد + مراجعة",الإعدادات!$B$2,IF(H16="مراجعة فقط",الإعدادات!$B$3,IF(H16="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="5">
-        <f>IF(A17="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A17,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C17" s="5">
-        <f>IF(A17="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A17,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="5">
-        <f>IF(E17="","",IF(AND(F17="نعم",G17="نعم"),"جرد + مراجعة",IF(F17="نعم","جرد فقط",IF(G17="نعم","مراجعة فقط",""))))</f>
-        <v/>
-      </c>
-      <c r="I17" s="9">
-        <f>IF(H17="جرد + مراجعة",الإعدادات!$B$2,IF(H17="مراجعة فقط",الإعدادات!$B$3,IF(H17="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="5">
-        <f>IF(A18="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A18,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C18" s="5">
-        <f>IF(A18="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A18,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="5">
-        <f>IF(E18="","",IF(AND(F18="نعم",G18="نعم"),"جرد + مراجعة",IF(F18="نعم","جرد فقط",IF(G18="نعم","مراجعة فقط",""))))</f>
-        <v/>
-      </c>
-      <c r="I18" s="9">
-        <f>IF(H18="جرد + مراجعة",الإعدادات!$B$2,IF(H18="مراجعة فقط",الإعدادات!$B$3,IF(H18="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="5">
-        <f>IF(A19="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A19,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C19" s="5">
-        <f>IF(A19="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A19,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H19" s="5">
         <f>IF(E19="","",IF(AND(F19="نعم",G19="نعم"),"جرد + مراجعة",IF(F19="نعم","جرد فقط",IF(G19="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2554,7 +2604,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="B20" s="5">
         <f>IF(A20="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A20,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2563,10 +2617,20 @@
         <f>IF(A20="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A20,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="D20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H20" s="5">
         <f>IF(E20="","",IF(AND(F20="نعم",G20="نعم"),"جرد + مراجعة",IF(F20="نعم","جرد فقط",IF(G20="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2577,7 +2641,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="B21" s="5">
         <f>IF(A21="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A21,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2586,10 +2654,20 @@
         <f>IF(A21="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A21,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="D21" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H21" s="5">
         <f>IF(E21="","",IF(AND(F21="نعم",G21="نعم"),"جرد + مراجعة",IF(F21="نعم","جرد فقط",IF(G21="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2600,7 +2678,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="B22" s="5">
         <f>IF(A22="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A22,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2609,10 +2691,20 @@
         <f>IF(A22="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A22,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="D22" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H22" s="5">
         <f>IF(E22="","",IF(AND(F22="نعم",G22="نعم"),"جرد + مراجعة",IF(F22="نعم","جرد فقط",IF(G22="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -2678,11 +2678,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="n"/>
       <c r="B22" s="5">
         <f>IF(A22="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A22,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2691,20 +2687,10 @@
         <f>IF(A22="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A22,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>د. أيمن حسين</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
       <c r="H22" s="5">
         <f>IF(E22="","",IF(AND(F22="نعم",G22="نعم"),"جرد + مراجعة",IF(F22="نعم","جرد فقط",IF(G22="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -685,7 +685,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
         <v/>
@@ -2678,7 +2682,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B22" s="5">
         <f>IF(A22="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A22,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2687,10 +2695,24 @@
         <f>IF(A22="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A22,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="D22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H22" s="5">
         <f>IF(E22="","",IF(AND(F22="نعم",G22="نعم"),"جرد + مراجعة",IF(F22="نعم","جرد فقط",IF(G22="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2701,7 +2723,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B23" s="5">
         <f>IF(A23="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A23,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2710,10 +2736,20 @@
         <f>IF(A23="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A23,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
+      <c r="D23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H23" s="5">
         <f>IF(E23="","",IF(AND(F23="نعم",G23="نعم"),"جرد + مراجعة",IF(F23="نعم","جرد فقط",IF(G23="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2724,7 +2760,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B24" s="5">
         <f>IF(A24="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A24,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2733,10 +2773,20 @@
         <f>IF(A24="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A24,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
+      <c r="D24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H24" s="5">
         <f>IF(E24="","",IF(AND(F24="نعم",G24="نعم"),"جرد + مراجعة",IF(F24="نعم","جرد فقط",IF(G24="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2747,7 +2797,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B25" s="5">
         <f>IF(A25="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A25,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2756,10 +2810,20 @@
         <f>IF(A25="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A25,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
+      <c r="D25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H25" s="5">
         <f>IF(E25="","",IF(AND(F25="نعم",G25="نعم"),"جرد + مراجعة",IF(F25="نعم","جرد فقط",IF(G25="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2770,7 +2834,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B26" s="5">
         <f>IF(A26="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A26,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2779,10 +2847,20 @@
         <f>IF(A26="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A26,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
+      <c r="D26" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H26" s="5">
         <f>IF(E26="","",IF(AND(F26="نعم",G26="نعم"),"جرد + مراجعة",IF(F26="نعم","جرد فقط",IF(G26="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2793,7 +2871,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B27" s="5">
         <f>IF(A27="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A27,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2802,10 +2884,24 @@
         <f>IF(A27="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A27,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
+      <c r="D27" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H27" s="5">
         <f>IF(E27="","",IF(AND(F27="نعم",G27="نعم"),"جرد + مراجعة",IF(F27="نعم","جرد فقط",IF(G27="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2816,7 +2912,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B28" s="5">
         <f>IF(A28="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A28,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2825,10 +2925,20 @@
         <f>IF(A28="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A28,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
+      <c r="D28" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H28" s="5">
         <f>IF(E28="","",IF(AND(F28="نعم",G28="نعم"),"جرد + مراجعة",IF(F28="نعم","جرد فقط",IF(G28="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2839,7 +2949,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B29" s="5">
         <f>IF(A29="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A29,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2848,10 +2962,20 @@
         <f>IF(A29="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A29,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="D29" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H29" s="5">
         <f>IF(E29="","",IF(AND(F29="نعم",G29="نعم"),"جرد + مراجعة",IF(F29="نعم","جرد فقط",IF(G29="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2862,7 +2986,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B30" s="5">
         <f>IF(A30="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A30,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2871,10 +2999,20 @@
         <f>IF(A30="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A30,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
+      <c r="D30" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H30" s="5">
         <f>IF(E30="","",IF(AND(F30="نعم",G30="نعم"),"جرد + مراجعة",IF(F30="نعم","جرد فقط",IF(G30="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -2885,7 +3023,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="B31" s="5">
         <f>IF(A31="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A31,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -2894,10 +3036,20 @@
         <f>IF(A31="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A31,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
+      <c r="D31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H31" s="5">
         <f>IF(E31="","",IF(AND(F31="نعم",G31="نعم"),"جرد + مراجعة",IF(F31="نعم","جرد فقط",IF(G31="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -3060,7 +3060,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B32" s="5">
         <f>IF(A32="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A32,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3069,10 +3073,24 @@
         <f>IF(A32="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A32,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
+      <c r="D32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H32" s="5">
         <f>IF(E32="","",IF(AND(F32="نعم",G32="نعم"),"جرد + مراجعة",IF(F32="نعم","جرد فقط",IF(G32="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3083,7 +3101,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B33" s="5">
         <f>IF(A33="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A33,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3092,10 +3114,20 @@
         <f>IF(A33="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A33,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
+      <c r="D33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H33" s="5">
         <f>IF(E33="","",IF(AND(F33="نعم",G33="نعم"),"جرد + مراجعة",IF(F33="نعم","جرد فقط",IF(G33="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3106,7 +3138,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B34" s="5">
         <f>IF(A34="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A34,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3115,10 +3151,20 @@
         <f>IF(A34="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A34,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
+      <c r="D34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H34" s="5">
         <f>IF(E34="","",IF(AND(F34="نعم",G34="نعم"),"جرد + مراجعة",IF(F34="نعم","جرد فقط",IF(G34="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3129,7 +3175,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n"/>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B35" s="5">
         <f>IF(A35="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A35,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3138,10 +3188,20 @@
         <f>IF(A35="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A35,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
+      <c r="D35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H35" s="5">
         <f>IF(E35="","",IF(AND(F35="نعم",G35="نعم"),"جرد + مراجعة",IF(F35="نعم","جرد فقط",IF(G35="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3152,7 +3212,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n"/>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B36" s="5">
         <f>IF(A36="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A36,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3161,10 +3225,24 @@
         <f>IF(A36="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A36,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
+      <c r="D36" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H36" s="5">
         <f>IF(E36="","",IF(AND(F36="نعم",G36="نعم"),"جرد + مراجعة",IF(F36="نعم","جرد فقط",IF(G36="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3175,7 +3253,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B37" s="5">
         <f>IF(A37="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A37,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3184,10 +3266,20 @@
         <f>IF(A37="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A37,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
+      <c r="D37" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H37" s="5">
         <f>IF(E37="","",IF(AND(F37="نعم",G37="نعم"),"جرد + مراجعة",IF(F37="نعم","جرد فقط",IF(G37="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3198,7 +3290,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B38" s="5">
         <f>IF(A38="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A38,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3207,10 +3303,20 @@
         <f>IF(A38="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A38,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
+      <c r="D38" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H38" s="5">
         <f>IF(E38="","",IF(AND(F38="نعم",G38="نعم"),"جرد + مراجعة",IF(F38="نعم","جرد فقط",IF(G38="نعم","مراجعة فقط",""))))</f>
         <v/>
@@ -3221,7 +3327,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B39" s="5">
         <f>IF(A39="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A39,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3230,10 +3340,20 @@
         <f>IF(A39="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A39,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
+      <c r="D39" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H39" s="5">
         <f>IF(E39="","",IF(AND(F39="نعم",G39="نعم"),"جرد + مراجعة",IF(F39="نعم","جرد فقط",IF(G39="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -3364,7 +3364,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B40" s="5">
         <f>IF(A40="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A40,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
@@ -3373,10 +3377,20 @@
         <f>IF(A40="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A40,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
         <v/>
       </c>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
+      <c r="D40" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H40" s="5">
         <f>IF(E40="","",IF(AND(F40="نعم",G40="نعم"),"جرد + مراجعة",IF(F40="نعم","جرد فقط",IF(G40="نعم","مراجعة فقط",""))))</f>
         <v/>

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>1800</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>1500</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
       </c>
       <c r="B6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -654,11 +654,11 @@
       </c>
       <c r="E6" s="5">
         <f>IF(A6="","",SUM(B6:D6))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="6">
         <f>IF(A6="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A6))</f>
-        <v>1700</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="7">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="8">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -953,11 +953,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -965,11 +965,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>6350</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="21">
@@ -980,7 +980,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>6350</v>
+        <v>7150</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1003,7 +1003,8 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1044,6 +1045,12 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>الخميس
+2026-10-01</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1073,9 +1080,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,F$1000)</f>
         <v>400</v>
       </c>
-      <c r="G2" s="6">
-        <f>SUM(B2:F2)</f>
-        <v>1800</v>
+      <c r="G2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="H2" s="6">
+        <f>SUM(B2:G2)</f>
+        <v>1950</v>
       </c>
     </row>
     <row r="3">
@@ -1103,9 +1114,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,F$1000)</f>
         <v>300</v>
       </c>
-      <c r="G3" s="6">
-        <f>SUM(B3:F3)</f>
-        <v>1500</v>
+      <c r="G3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="H3" s="6">
+        <f>SUM(B3:G3)</f>
+        <v>1650</v>
       </c>
     </row>
     <row r="4">
@@ -1133,9 +1148,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,F$1000)</f>
         <v>300</v>
       </c>
-      <c r="G4" s="6">
-        <f>SUM(B4:F4)</f>
-        <v>1700</v>
+      <c r="G4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>200</v>
+      </c>
+      <c r="H4" s="6">
+        <f>SUM(B4:G4)</f>
+        <v>1900</v>
       </c>
     </row>
     <row r="5">
@@ -1163,9 +1182,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,F$1000)</f>
         <v>300</v>
       </c>
-      <c r="G5" s="6">
-        <f>SUM(B5:F5)</f>
-        <v>900</v>
+      <c r="G5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="H5" s="6">
+        <f>SUM(B5:G5)</f>
+        <v>1050</v>
       </c>
     </row>
     <row r="6">
@@ -1193,9 +1216,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,F$1000)</f>
         <v>150</v>
       </c>
-      <c r="G6" s="6">
-        <f>SUM(B6:F6)</f>
-        <v>450</v>
+      <c r="G6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="H6" s="6">
+        <f>SUM(B6:G6)</f>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -1226,7 +1253,11 @@
       </c>
       <c r="G7" s="8">
         <f>SUM(G2:G6)</f>
-        <v>6350</v>
+        <v>800</v>
+      </c>
+      <c r="H7" s="8">
+        <f>SUM(H2:H6)</f>
+        <v>7150</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1253,6 +1284,11 @@
       <c r="F1000" t="inlineStr">
         <is>
           <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -3678,118 +3714,192 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="B41" s="5" t="str">
         <f>IF(A41="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A41,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C41" s="5" t="str">
         <f>IF(A41="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A41,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H41" s="5" t="str">
         <f>IF(E41="","",IF(AND(F41="نعم",G41="نعم"),"جرد + مراجعة",IF(F41="نعم","جرد فقط",IF(G41="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I41" s="9">
         <f>IF(H41="جرد + مراجعة",الإعدادات!$B$2,IF(H41="مراجعة فقط",الإعدادات!$B$3,IF(H41="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="B42" s="5" t="str">
         <f>IF(A42="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A42,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C42" s="5" t="str">
         <f>IF(A42="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A42,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H42" s="5" t="str">
         <f>IF(E42="","",IF(AND(F42="نعم",G42="نعم"),"جرد + مراجعة",IF(F42="نعم","جرد فقط",IF(G42="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I42" s="9">
         <f>IF(H42="جرد + مراجعة",الإعدادات!$B$2,IF(H42="مراجعة فقط",الإعدادات!$B$3,IF(H42="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="B43" s="5" t="str">
         <f>IF(A43="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A43,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C43" s="5" t="str">
         <f>IF(A43="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A43,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H43" s="5" t="str">
         <f>IF(E43="","",IF(AND(F43="نعم",G43="نعم"),"جرد + مراجعة",IF(F43="نعم","جرد فقط",IF(G43="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I43" s="9">
         <f>IF(H43="جرد + مراجعة",الإعدادات!$B$2,IF(H43="مراجعة فقط",الإعدادات!$B$3,IF(H43="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="str">
         <f>IF(A44="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A44,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C44" s="5" t="str">
         <f>IF(A44="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A44,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H44" s="5" t="str">
         <f>IF(E44="","",IF(AND(F44="نعم",G44="نعم"),"جرد + مراجعة",IF(F44="نعم","جرد فقط",IF(G44="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I44" s="9">
         <f>IF(H44="جرد + مراجعة",الإعدادات!$B$2,IF(H44="مراجعة فقط",الإعدادات!$B$3,IF(H44="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="B45" s="5" t="str">
         <f>IF(A45="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A45,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C45" s="5" t="str">
         <f>IF(A45="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A45,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H45" s="5" t="str">
         <f>IF(E45="","",IF(AND(F45="نعم",G45="نعم"),"جرد + مراجعة",IF(F45="نعم","جرد فقط",IF(G45="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I45" s="9">
         <f>IF(H45="جرد + مراجعة",الإعدادات!$B$2,IF(H45="مراجعة فقط",الإعدادات!$B$3,IF(H45="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>1950</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>1650</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="6">
@@ -646,7 +646,7 @@
       </c>
       <c r="C6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -654,11 +654,11 @@
       </c>
       <c r="E6" s="5">
         <f>IF(A6="","",SUM(B6:D6))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6">
         <f>IF(A6="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A6))</f>
-        <v>1900</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="7">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>1050</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9">
@@ -953,11 +953,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -965,11 +965,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>7150</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="21">
@@ -980,7 +980,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>7150</v>
+        <v>7950</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1004,7 +1004,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1051,6 +1052,12 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
+          <t>الجمعة
+2026-10-02</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1084,9 +1091,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,G$1000)</f>
         <v>150</v>
       </c>
-      <c r="H2" s="6">
-        <f>SUM(B2:G2)</f>
-        <v>1950</v>
+      <c r="H2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>200</v>
+      </c>
+      <c r="I2" s="6">
+        <f>SUM(B2:H2)</f>
+        <v>2150</v>
       </c>
     </row>
     <row r="3">
@@ -1118,9 +1129,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,G$1000)</f>
         <v>150</v>
       </c>
-      <c r="H3" s="6">
-        <f>SUM(B3:G3)</f>
-        <v>1650</v>
+      <c r="H3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="I3" s="6">
+        <f>SUM(B3:H3)</f>
+        <v>1800</v>
       </c>
     </row>
     <row r="4">
@@ -1152,9 +1167,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,G$1000)</f>
         <v>200</v>
       </c>
-      <c r="H4" s="6">
-        <f>SUM(B4:G4)</f>
-        <v>1900</v>
+      <c r="H4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="I4" s="6">
+        <f>SUM(B4:H4)</f>
+        <v>2050</v>
       </c>
     </row>
     <row r="5">
@@ -1186,9 +1205,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,G$1000)</f>
         <v>150</v>
       </c>
-      <c r="H5" s="6">
-        <f>SUM(B5:G5)</f>
-        <v>1050</v>
+      <c r="H5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="I5" s="6">
+        <f>SUM(B5:H5)</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -1220,9 +1243,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,G$1000)</f>
         <v>150</v>
       </c>
-      <c r="H6" s="6">
-        <f>SUM(B6:G6)</f>
-        <v>600</v>
+      <c r="H6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="I6" s="6">
+        <f>SUM(B6:H6)</f>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1257,7 +1284,11 @@
       </c>
       <c r="H7" s="8">
         <f>SUM(H2:H6)</f>
-        <v>7150</v>
+        <v>800</v>
+      </c>
+      <c r="I7" s="8">
+        <f>SUM(I2:I6)</f>
+        <v>7950</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1289,6 +1320,11 @@
       <c r="G1000" t="inlineStr">
         <is>
           <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -3903,118 +3939,192 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n"/>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="B46" s="5" t="str">
         <f>IF(A46="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A46,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C46" s="5" t="str">
         <f>IF(A46="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A46,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H46" s="5" t="str">
         <f>IF(E46="","",IF(AND(F46="نعم",G46="نعم"),"جرد + مراجعة",IF(F46="نعم","جرد فقط",IF(G46="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I46" s="9">
         <f>IF(H46="جرد + مراجعة",الإعدادات!$B$2,IF(H46="مراجعة فقط",الإعدادات!$B$3,IF(H46="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="B47" s="5" t="str">
         <f>IF(A47="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A47,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C47" s="5" t="str">
         <f>IF(A47="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A47,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H47" s="5" t="str">
         <f>IF(E47="","",IF(AND(F47="نعم",G47="نعم"),"جرد + مراجعة",IF(F47="نعم","جرد فقط",IF(G47="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I47" s="9">
         <f>IF(H47="جرد + مراجعة",الإعدادات!$B$2,IF(H47="مراجعة فقط",الإعدادات!$B$3,IF(H47="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n"/>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="B48" s="5" t="str">
         <f>IF(A48="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A48,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C48" s="5" t="str">
         <f>IF(A48="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A48,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H48" s="5" t="str">
         <f>IF(E48="","",IF(AND(F48="نعم",G48="نعم"),"جرد + مراجعة",IF(F48="نعم","جرد فقط",IF(G48="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I48" s="9">
         <f>IF(H48="جرد + مراجعة",الإعدادات!$B$2,IF(H48="مراجعة فقط",الإعدادات!$B$3,IF(H48="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n"/>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="B49" s="5" t="str">
         <f>IF(A49="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A49,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C49" s="5" t="str">
         <f>IF(A49="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A49,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H49" s="5" t="str">
         <f>IF(E49="","",IF(AND(F49="نعم",G49="نعم"),"جرد + مراجعة",IF(F49="نعم","جرد فقط",IF(G49="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I49" s="9">
         <f>IF(H49="جرد + مراجعة",الإعدادات!$B$2,IF(H49="مراجعة فقط",الإعدادات!$B$3,IF(H49="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n"/>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="B50" s="5" t="str">
         <f>IF(A50="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$28,MATCH(A50,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C50" s="5" t="str">
         <f>IF(A50="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$28,MATCH(A50,'جدول الجرد'!$B$2:$B$28,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H50" s="5" t="str">
         <f>IF(E50="","",IF(AND(F50="نعم",G50="نعم"),"جرد + مراجعة",IF(F50="نعم","جرد فقط",IF(G50="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I50" s="9">
         <f>IF(H50="جرد + مراجعة",الإعدادات!$B$2,IF(H50="مراجعة فقط",الإعدادات!$B$3,IF(H50="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>2550</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="6">
@@ -646,7 +646,7 @@
       </c>
       <c r="C6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -654,11 +654,11 @@
       </c>
       <c r="E6" s="5">
         <f>IF(A6="","",SUM(B6:D6))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="6">
         <f>IF(A6="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A6))</f>
-        <v>1500</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="7">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>900</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="8">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>2050</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="9">
@@ -953,11 +953,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -965,11 +965,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>9100</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="21">
@@ -980,7 +980,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>9100</v>
+        <v>9900</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1006,7 +1006,8 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1065,6 +1066,12 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
+          <t>السبت
+2026-10-03</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1106,9 +1113,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,I$1000)</f>
         <v>200</v>
       </c>
-      <c r="J2" s="6">
-        <f>SUM(B2:I2)</f>
-        <v>2550</v>
+      <c r="J2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="K2" s="6">
+        <f>SUM(B2:J2)</f>
+        <v>2700</v>
       </c>
     </row>
     <row r="3">
@@ -1148,9 +1159,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,I$1000)</f>
         <v>150</v>
       </c>
-      <c r="J3" s="6">
-        <f>SUM(B3:I3)</f>
-        <v>2100</v>
+      <c r="J3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="K3" s="6">
+        <f>SUM(B3:J3)</f>
+        <v>2250</v>
       </c>
     </row>
     <row r="4">
@@ -1190,9 +1205,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,I$1000)</f>
         <v>150</v>
       </c>
-      <c r="J4" s="6">
-        <f>SUM(B4:I4)</f>
-        <v>1500</v>
+      <c r="J4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="K4" s="6">
+        <f>SUM(B4:J4)</f>
+        <v>1650</v>
       </c>
     </row>
     <row r="5">
@@ -1232,9 +1251,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,I$1000)</f>
         <v>150</v>
       </c>
-      <c r="J5" s="6">
-        <f>SUM(B5:I5)</f>
-        <v>900</v>
+      <c r="J5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="K5" s="6">
+        <f>SUM(B5:J5)</f>
+        <v>1050</v>
       </c>
     </row>
     <row r="6">
@@ -1274,9 +1297,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,I$1000)</f>
         <v>150</v>
       </c>
-      <c r="J6" s="6">
-        <f>SUM(B6:I6)</f>
-        <v>2050</v>
+      <c r="J6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>200</v>
+      </c>
+      <c r="K6" s="6">
+        <f>SUM(B6:J6)</f>
+        <v>2250</v>
       </c>
     </row>
     <row r="7">
@@ -1319,7 +1346,11 @@
       </c>
       <c r="J7" s="8">
         <f>SUM(J2:J6)</f>
-        <v>9100</v>
+        <v>800</v>
+      </c>
+      <c r="K7" s="8">
+        <f>SUM(K2:K6)</f>
+        <v>9900</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1361,6 +1392,11 @@
       <c r="I1000" t="inlineStr">
         <is>
           <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4458,118 +4494,192 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n"/>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="B58" s="5" t="str">
         <f>IF(A58="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A58,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C58" s="5" t="str">
         <f>IF(A58="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A58,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H58" s="5" t="str">
         <f>IF(E58="","",IF(AND(F58="نعم",G58="نعم"),"جرد + مراجعة",IF(F58="نعم","جرد فقط",IF(G58="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I58" s="9">
         <f>IF(H58="جرد + مراجعة",الإعدادات!$B$2,IF(H58="مراجعة فقط",الإعدادات!$B$3,IF(H58="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="B59" s="5" t="str">
         <f>IF(A59="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A59,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C59" s="5" t="str">
         <f>IF(A59="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A59,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H59" s="5" t="str">
         <f>IF(E59="","",IF(AND(F59="نعم",G59="نعم"),"جرد + مراجعة",IF(F59="نعم","جرد فقط",IF(G59="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I59" s="9">
         <f>IF(H59="جرد + مراجعة",الإعدادات!$B$2,IF(H59="مراجعة فقط",الإعدادات!$B$3,IF(H59="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n"/>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="B60" s="5" t="str">
         <f>IF(A60="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A60,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C60" s="5" t="str">
         <f>IF(A60="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A60,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H60" s="5" t="str">
         <f>IF(E60="","",IF(AND(F60="نعم",G60="نعم"),"جرد + مراجعة",IF(F60="نعم","جرد فقط",IF(G60="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I60" s="9">
         <f>IF(H60="جرد + مراجعة",الإعدادات!$B$2,IF(H60="مراجعة فقط",الإعدادات!$B$3,IF(H60="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n"/>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="B61" s="5" t="str">
         <f>IF(A61="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A61,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C61" s="5" t="str">
         <f>IF(A61="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A61,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>د. أيمن حسين</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H61" s="5" t="str">
         <f>IF(E61="","",IF(AND(F61="نعم",G61="نعم"),"جرد + مراجعة",IF(F61="نعم","جرد فقط",IF(G61="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I61" s="9">
         <f>IF(H61="جرد + مراجعة",الإعدادات!$B$2,IF(H61="مراجعة فقط",الإعدادات!$B$3,IF(H61="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n"/>
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="B62" s="5" t="str">
         <f>IF(A62="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A62,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C62" s="5" t="str">
         <f>IF(A62="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A62,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
+        <v>الدلم</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H62" s="5" t="str">
         <f>IF(E62="","",IF(AND(F62="نعم",G62="نعم"),"جرد + مراجعة",IF(F62="نعم","جرد فقط",IF(G62="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I62" s="9">
         <f>IF(H62="جرد + مراجعة",الإعدادات!$B$2,IF(H62="مراجعة فقط",الإعدادات!$B$3,IF(H62="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>2700</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>2250</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>1050</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="8">
@@ -716,26 +716,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="5" t="str">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v/>
-      </c>
-      <c r="D9" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
-        <v/>
-      </c>
-      <c r="E9" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v/>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -953,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -965,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>9900</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="21">
@@ -980,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>9900</v>
+        <v>11200</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1007,7 +1011,8 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1072,6 +1077,12 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>الأحد
+2026-10-04</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1117,9 +1128,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,J$1000)</f>
         <v>150</v>
       </c>
-      <c r="K2" s="6">
-        <f>SUM(B2:J2)</f>
-        <v>2700</v>
+      <c r="K2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="L2" s="6">
+        <f>SUM(B2:K2)</f>
+        <v>3100</v>
       </c>
     </row>
     <row r="3">
@@ -1163,9 +1178,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,J$1000)</f>
         <v>150</v>
       </c>
-      <c r="K3" s="6">
-        <f>SUM(B3:J3)</f>
-        <v>2250</v>
+      <c r="K3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="L3" s="6">
+        <f>SUM(B3:K3)</f>
+        <v>2550</v>
       </c>
     </row>
     <row r="4">
@@ -1209,8 +1228,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,J$1000)</f>
         <v>150</v>
       </c>
-      <c r="K4" s="6">
-        <f>SUM(B4:J4)</f>
+      <c r="K4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <f>SUM(B4:K4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1255,9 +1278,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,J$1000)</f>
         <v>150</v>
       </c>
-      <c r="K5" s="6">
-        <f>SUM(B5:J5)</f>
-        <v>1050</v>
+      <c r="K5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="L5" s="6">
+        <f>SUM(B5:K5)</f>
+        <v>1350</v>
       </c>
     </row>
     <row r="6">
@@ -1301,56 +1328,114 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,J$1000)</f>
         <v>200</v>
       </c>
-      <c r="K6" s="6">
-        <f>SUM(B6:J6)</f>
+      <c r="K6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <f>SUM(B6:K6)</f>
         <v>2250</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="10" t="str">
+        <f>الملخص!A9</f>
+        <v>د. محمد جمال</v>
+      </c>
+      <c r="B7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,B$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,C$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,D$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,E$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,F$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,I$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="L7" s="6">
+        <f>SUM(B7:K7)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B7" s="8">
-        <f>SUM(B2:B6)</f>
+      <c r="B8" s="8">
+        <f>SUM(B2:B7)</f>
         <v>1150</v>
       </c>
-      <c r="C7" s="8">
-        <f>SUM(C2:C6)</f>
+      <c r="C8" s="8">
+        <f>SUM(C2:C7)</f>
         <v>1000</v>
       </c>
-      <c r="D7" s="8">
-        <f>SUM(D2:D6)</f>
+      <c r="D8" s="8">
+        <f>SUM(D2:D7)</f>
         <v>1150</v>
       </c>
-      <c r="E7" s="8">
-        <f>SUM(E2:E6)</f>
+      <c r="E8" s="8">
+        <f>SUM(E2:E7)</f>
         <v>1150</v>
       </c>
-      <c r="F7" s="8">
-        <f>SUM(F2:F6)</f>
+      <c r="F8" s="8">
+        <f>SUM(F2:F7)</f>
         <v>1600</v>
       </c>
-      <c r="G7" s="8">
-        <f>SUM(G2:G6)</f>
+      <c r="G8" s="8">
+        <f>SUM(G2:G7)</f>
         <v>1450</v>
       </c>
-      <c r="H7" s="8">
-        <f>SUM(H2:H6)</f>
+      <c r="H8" s="8">
+        <f>SUM(H2:H7)</f>
         <v>800</v>
       </c>
-      <c r="I7" s="8">
-        <f>SUM(I2:I6)</f>
+      <c r="I8" s="8">
+        <f>SUM(I2:I7)</f>
         <v>800</v>
       </c>
-      <c r="J7" s="8">
-        <f>SUM(J2:J6)</f>
+      <c r="J8" s="8">
+        <f>SUM(J2:J7)</f>
         <v>800</v>
       </c>
-      <c r="K7" s="8">
-        <f>SUM(K2:K6)</f>
-        <v>9900</v>
+      <c r="K8" s="8">
+        <f>SUM(K2:K7)</f>
+        <v>1300</v>
+      </c>
+      <c r="L8" s="8">
+        <f>SUM(L2:L7)</f>
+        <v>11200</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1397,6 +1482,11 @@
       <c r="J1000" t="inlineStr">
         <is>
           <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4683,187 +4773,307 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n"/>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B63" s="5" t="str">
         <f>IF(A63="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A63,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C63" s="5" t="str">
         <f>IF(A63="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A63,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H63" s="5" t="str">
         <f>IF(E63="","",IF(AND(F63="نعم",G63="نعم"),"جرد + مراجعة",IF(F63="نعم","جرد فقط",IF(G63="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I63" s="9">
         <f>IF(H63="جرد + مراجعة",الإعدادات!$B$2,IF(H63="مراجعة فقط",الإعدادات!$B$3,IF(H63="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n"/>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B64" s="5" t="str">
         <f>IF(A64="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A64,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C64" s="5" t="str">
         <f>IF(A64="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A64,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H64" s="5" t="str">
         <f>IF(E64="","",IF(AND(F64="نعم",G64="نعم"),"جرد + مراجعة",IF(F64="نعم","جرد فقط",IF(G64="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I64" s="9">
         <f>IF(H64="جرد + مراجعة",الإعدادات!$B$2,IF(H64="مراجعة فقط",الإعدادات!$B$3,IF(H64="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n"/>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B65" s="5" t="str">
         <f>IF(A65="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A65,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C65" s="5" t="str">
         <f>IF(A65="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A65,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H65" s="5" t="str">
         <f>IF(E65="","",IF(AND(F65="نعم",G65="نعم"),"جرد + مراجعة",IF(F65="نعم","جرد فقط",IF(G65="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I65" s="9">
         <f>IF(H65="جرد + مراجعة",الإعدادات!$B$2,IF(H65="مراجعة فقط",الإعدادات!$B$3,IF(H65="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n"/>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B66" s="5" t="str">
         <f>IF(A66="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A66,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C66" s="5" t="str">
         <f>IF(A66="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A66,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H66" s="5" t="str">
         <f>IF(E66="","",IF(AND(F66="نعم",G66="نعم"),"جرد + مراجعة",IF(F66="نعم","جرد فقط",IF(G66="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I66" s="9">
         <f>IF(H66="جرد + مراجعة",الإعدادات!$B$2,IF(H66="مراجعة فقط",الإعدادات!$B$3,IF(H66="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n"/>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B67" s="5" t="str">
         <f>IF(A67="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A67,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C67" s="5" t="str">
         <f>IF(A67="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A67,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H67" s="5" t="str">
         <f>IF(E67="","",IF(AND(F67="نعم",G67="نعم"),"جرد + مراجعة",IF(F67="نعم","جرد فقط",IF(G67="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I67" s="9">
         <f>IF(H67="جرد + مراجعة",الإعدادات!$B$2,IF(H67="مراجعة فقط",الإعدادات!$B$3,IF(H67="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n"/>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B68" s="5" t="str">
         <f>IF(A68="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A68,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C68" s="5" t="str">
         <f>IF(A68="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A68,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H68" s="5" t="str">
         <f>IF(E68="","",IF(AND(F68="نعم",G68="نعم"),"جرد + مراجعة",IF(F68="نعم","جرد فقط",IF(G68="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I68" s="9">
         <f>IF(H68="جرد + مراجعة",الإعدادات!$B$2,IF(H68="مراجعة فقط",الإعدادات!$B$3,IF(H68="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n"/>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B69" s="5" t="str">
         <f>IF(A69="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A69,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C69" s="5" t="str">
         <f>IF(A69="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A69,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H69" s="5" t="str">
         <f>IF(E69="","",IF(AND(F69="نعم",G69="نعم"),"جرد + مراجعة",IF(F69="نعم","جرد فقط",IF(G69="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I69" s="9">
         <f>IF(H69="جرد + مراجعة",الإعدادات!$B$2,IF(H69="مراجعة فقط",الإعدادات!$B$3,IF(H69="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n"/>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="B70" s="5" t="str">
         <f>IF(A70="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A70,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C70" s="5" t="str">
         <f>IF(A70="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A70,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="4" t="n"/>
+        <v>الحوطة</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H70" s="5" t="str">
         <f>IF(E70="","",IF(AND(F70="نعم",G70="نعم"),"جرد + مراجعة",IF(F70="نعم","جرد فقط",IF(G70="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I70" s="9">
         <f>IF(H70="جرد + مراجعة",الإعدادات!$B$2,IF(H70="مراجعة فقط",الإعدادات!$B$3,IF(H70="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>3100</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>2550</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>1350</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>300</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>11200</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>11200</v>
+        <v>12500</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:M1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1012,8 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1083,6 +1084,12 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>الاثنين
+2026-10-05</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1132,9 +1139,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,K$1000)</f>
         <v>400</v>
       </c>
-      <c r="L2" s="6">
-        <f>SUM(B2:K2)</f>
-        <v>3100</v>
+      <c r="L2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,L$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="M2" s="6">
+        <f>SUM(B2:L2)</f>
+        <v>3400</v>
       </c>
     </row>
     <row r="3">
@@ -1182,9 +1193,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,K$1000)</f>
         <v>300</v>
       </c>
-      <c r="L3" s="6">
-        <f>SUM(B3:K3)</f>
-        <v>2550</v>
+      <c r="L3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,L$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="M3" s="6">
+        <f>SUM(B3:L3)</f>
+        <v>2950</v>
       </c>
     </row>
     <row r="4">
@@ -1232,8 +1247,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,K$1000)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="6">
-        <f>SUM(B4:K4)</f>
+      <c r="L4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,L$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <f>SUM(B4:L4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1282,9 +1301,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,K$1000)</f>
         <v>300</v>
       </c>
-      <c r="L5" s="6">
-        <f>SUM(B5:K5)</f>
-        <v>1350</v>
+      <c r="L5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,L$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="M5" s="6">
+        <f>SUM(B5:L5)</f>
+        <v>1650</v>
       </c>
     </row>
     <row r="6">
@@ -1332,8 +1355,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,K$1000)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="6">
-        <f>SUM(B6:K6)</f>
+      <c r="L6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,L$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <f>SUM(B6:L6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1382,9 +1409,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,K$1000)</f>
         <v>300</v>
       </c>
-      <c r="L7" s="6">
-        <f>SUM(B7:K7)</f>
+      <c r="L7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,L$1000)</f>
         <v>300</v>
+      </c>
+      <c r="M7" s="6">
+        <f>SUM(B7:L7)</f>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1435,7 +1466,11 @@
       </c>
       <c r="L8" s="8">
         <f>SUM(L2:L7)</f>
-        <v>11200</v>
+        <v>1300</v>
+      </c>
+      <c r="M8" s="8">
+        <f>SUM(M2:M7)</f>
+        <v>12500</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1487,6 +1522,11 @@
       <c r="K1000" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -5077,187 +5117,307 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n"/>
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B71" s="5" t="str">
         <f>IF(A71="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A71,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C71" s="5" t="str">
         <f>IF(A71="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A71,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H71" s="5" t="str">
         <f>IF(E71="","",IF(AND(F71="نعم",G71="نعم"),"جرد + مراجعة",IF(F71="نعم","جرد فقط",IF(G71="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I71" s="9">
         <f>IF(H71="جرد + مراجعة",الإعدادات!$B$2,IF(H71="مراجعة فقط",الإعدادات!$B$3,IF(H71="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n"/>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B72" s="5" t="str">
         <f>IF(A72="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A72,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C72" s="5" t="str">
         <f>IF(A72="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A72,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H72" s="5" t="str">
         <f>IF(E72="","",IF(AND(F72="نعم",G72="نعم"),"جرد + مراجعة",IF(F72="نعم","جرد فقط",IF(G72="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I72" s="9">
         <f>IF(H72="جرد + مراجعة",الإعدادات!$B$2,IF(H72="مراجعة فقط",الإعدادات!$B$3,IF(H72="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n"/>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B73" s="5" t="str">
         <f>IF(A73="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A73,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C73" s="5" t="str">
         <f>IF(A73="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A73,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H73" s="5" t="str">
         <f>IF(E73="","",IF(AND(F73="نعم",G73="نعم"),"جرد + مراجعة",IF(F73="نعم","جرد فقط",IF(G73="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I73" s="9">
         <f>IF(H73="جرد + مراجعة",الإعدادات!$B$2,IF(H73="مراجعة فقط",الإعدادات!$B$3,IF(H73="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n"/>
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="str">
         <f>IF(A74="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A74,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C74" s="5" t="str">
         <f>IF(A74="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A74,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H74" s="5" t="str">
         <f>IF(E74="","",IF(AND(F74="نعم",G74="نعم"),"جرد + مراجعة",IF(F74="نعم","جرد فقط",IF(G74="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I74" s="9">
         <f>IF(H74="جرد + مراجعة",الإعدادات!$B$2,IF(H74="مراجعة فقط",الإعدادات!$B$3,IF(H74="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n"/>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B75" s="5" t="str">
         <f>IF(A75="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A75,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C75" s="5" t="str">
         <f>IF(A75="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A75,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H75" s="5" t="str">
         <f>IF(E75="","",IF(AND(F75="نعم",G75="نعم"),"جرد + مراجعة",IF(F75="نعم","جرد فقط",IF(G75="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I75" s="9">
         <f>IF(H75="جرد + مراجعة",الإعدادات!$B$2,IF(H75="مراجعة فقط",الإعدادات!$B$3,IF(H75="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n"/>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B76" s="5" t="str">
         <f>IF(A76="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A76,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C76" s="5" t="str">
         <f>IF(A76="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A76,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H76" s="5" t="str">
         <f>IF(E76="","",IF(AND(F76="نعم",G76="نعم"),"جرد + مراجعة",IF(F76="نعم","جرد فقط",IF(G76="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I76" s="9">
         <f>IF(H76="جرد + مراجعة",الإعدادات!$B$2,IF(H76="مراجعة فقط",الإعدادات!$B$3,IF(H76="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n"/>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="str">
         <f>IF(A77="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A77,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C77" s="5" t="str">
         <f>IF(A77="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A77,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H77" s="5" t="str">
         <f>IF(E77="","",IF(AND(F77="نعم",G77="نعم"),"جرد + مراجعة",IF(F77="نعم","جرد فقط",IF(G77="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I77" s="9">
         <f>IF(H77="جرد + مراجعة",الإعدادات!$B$2,IF(H77="مراجعة فقط",الإعدادات!$B$3,IF(H77="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n"/>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="B78" s="5" t="str">
         <f>IF(A78="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A78,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C78" s="5" t="str">
         <f>IF(A78="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A78,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="4" t="n"/>
-      <c r="G78" s="4" t="n"/>
+        <v>الأفلاج</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H78" s="5" t="str">
         <f>IF(E78="","",IF(AND(F78="نعم",G78="نعم"),"جرد + مراجعة",IF(F78="نعم","جرد فقط",IF(G78="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I78" s="9">
         <f>IF(H78="جرد + مراجعة",الإعدادات!$B$2,IF(H78="مراجعة فقط",الإعدادات!$B$3,IF(H78="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>3400</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>2950</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>1650</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>12500</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>12500</v>
+        <v>13800</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1000"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1013,7 +1013,8 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1090,6 +1091,12 @@
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
+          <t>الثلاثاء
+2026-10-06</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1143,9 +1150,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,L$1000)</f>
         <v>300</v>
       </c>
-      <c r="M2" s="6">
-        <f>SUM(B2:L2)</f>
-        <v>3400</v>
+      <c r="M2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="N2" s="6">
+        <f>SUM(B2:M2)</f>
+        <v>3800</v>
       </c>
     </row>
     <row r="3">
@@ -1197,9 +1208,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,L$1000)</f>
         <v>400</v>
       </c>
-      <c r="M3" s="6">
-        <f>SUM(B3:L3)</f>
-        <v>2950</v>
+      <c r="M3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="N3" s="6">
+        <f>SUM(B3:M3)</f>
+        <v>3250</v>
       </c>
     </row>
     <row r="4">
@@ -1251,8 +1266,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,L$1000)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="6">
-        <f>SUM(B4:L4)</f>
+      <c r="M4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>SUM(B4:M4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1305,9 +1324,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,L$1000)</f>
         <v>300</v>
       </c>
-      <c r="M5" s="6">
-        <f>SUM(B5:L5)</f>
-        <v>1650</v>
+      <c r="M5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="N5" s="6">
+        <f>SUM(B5:M5)</f>
+        <v>1950</v>
       </c>
     </row>
     <row r="6">
@@ -1359,8 +1382,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,L$1000)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="6">
-        <f>SUM(B6:L6)</f>
+      <c r="M6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <f>SUM(B6:M6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1413,9 +1440,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,L$1000)</f>
         <v>300</v>
       </c>
-      <c r="M7" s="6">
-        <f>SUM(B7:L7)</f>
-        <v>600</v>
+      <c r="M7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="N7" s="6">
+        <f>SUM(B7:M7)</f>
+        <v>900</v>
       </c>
     </row>
     <row r="8">
@@ -1470,7 +1501,11 @@
       </c>
       <c r="M8" s="8">
         <f>SUM(M2:M7)</f>
-        <v>12500</v>
+        <v>1300</v>
+      </c>
+      <c r="N8" s="8">
+        <f>SUM(N2:N7)</f>
+        <v>13800</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1527,6 +1562,11 @@
       <c r="L1000" t="inlineStr">
         <is>
           <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="M1000" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5421,187 +5461,307 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n"/>
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B79" s="5" t="str">
         <f>IF(A79="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A79,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C79" s="5" t="str">
         <f>IF(A79="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A79,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H79" s="5" t="str">
         <f>IF(E79="","",IF(AND(F79="نعم",G79="نعم"),"جرد + مراجعة",IF(F79="نعم","جرد فقط",IF(G79="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I79" s="9">
         <f>IF(H79="جرد + مراجعة",الإعدادات!$B$2,IF(H79="مراجعة فقط",الإعدادات!$B$3,IF(H79="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n"/>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B80" s="5" t="str">
         <f>IF(A80="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A80,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C80" s="5" t="str">
         <f>IF(A80="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A80,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H80" s="5" t="str">
         <f>IF(E80="","",IF(AND(F80="نعم",G80="نعم"),"جرد + مراجعة",IF(F80="نعم","جرد فقط",IF(G80="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I80" s="9">
         <f>IF(H80="جرد + مراجعة",الإعدادات!$B$2,IF(H80="مراجعة فقط",الإعدادات!$B$3,IF(H80="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B81" s="5" t="str">
         <f>IF(A81="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A81,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C81" s="5" t="str">
         <f>IF(A81="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A81,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H81" s="5" t="str">
         <f>IF(E81="","",IF(AND(F81="نعم",G81="نعم"),"جرد + مراجعة",IF(F81="نعم","جرد فقط",IF(G81="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I81" s="9">
         <f>IF(H81="جرد + مراجعة",الإعدادات!$B$2,IF(H81="مراجعة فقط",الإعدادات!$B$3,IF(H81="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n"/>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B82" s="5" t="str">
         <f>IF(A82="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A82,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C82" s="5" t="str">
         <f>IF(A82="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A82,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H82" s="5" t="str">
         <f>IF(E82="","",IF(AND(F82="نعم",G82="نعم"),"جرد + مراجعة",IF(F82="نعم","جرد فقط",IF(G82="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I82" s="9">
         <f>IF(H82="جرد + مراجعة",الإعدادات!$B$2,IF(H82="مراجعة فقط",الإعدادات!$B$3,IF(H82="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n"/>
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B83" s="5" t="str">
         <f>IF(A83="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A83,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C83" s="5" t="str">
         <f>IF(A83="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A83,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H83" s="5" t="str">
         <f>IF(E83="","",IF(AND(F83="نعم",G83="نعم"),"جرد + مراجعة",IF(F83="نعم","جرد فقط",IF(G83="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I83" s="9">
         <f>IF(H83="جرد + مراجعة",الإعدادات!$B$2,IF(H83="مراجعة فقط",الإعدادات!$B$3,IF(H83="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n"/>
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B84" s="5" t="str">
         <f>IF(A84="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A84,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C84" s="5" t="str">
         <f>IF(A84="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A84,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H84" s="5" t="str">
         <f>IF(E84="","",IF(AND(F84="نعم",G84="نعم"),"جرد + مراجعة",IF(F84="نعم","جرد فقط",IF(G84="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I84" s="9">
         <f>IF(H84="جرد + مراجعة",الإعدادات!$B$2,IF(H84="مراجعة فقط",الإعدادات!$B$3,IF(H84="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n"/>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B85" s="5" t="str">
         <f>IF(A85="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A85,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C85" s="5" t="str">
         <f>IF(A85="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A85,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="4" t="n"/>
-      <c r="G85" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H85" s="5" t="str">
         <f>IF(E85="","",IF(AND(F85="نعم",G85="نعم"),"جرد + مراجعة",IF(F85="نعم","جرد فقط",IF(G85="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I85" s="9">
         <f>IF(H85="جرد + مراجعة",الإعدادات!$B$2,IF(H85="مراجعة فقط",الإعدادات!$B$3,IF(H85="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n"/>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="B86" s="5" t="str">
         <f>IF(A86="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A86,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C86" s="5" t="str">
         <f>IF(A86="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A86,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
+        <v>السليل</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H86" s="5" t="str">
         <f>IF(E86="","",IF(AND(F86="نعم",G86="نعم"),"جرد + مراجعة",IF(F86="نعم","جرد فقط",IF(G86="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I86" s="9">
         <f>IF(H86="جرد + مراجعة",الإعدادات!$B$2,IF(H86="مراجعة فقط",الإعدادات!$B$3,IF(H86="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>3800</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>3250</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>1950</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>900</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>13800</v>
+        <v>15100</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>13800</v>
+        <v>15100</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1000"/>
+  <dimension ref="A1:O1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1014,7 +1014,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1097,6 +1098,12 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>الأربعاء
+2026-10-07</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1154,9 +1161,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,M$1000)</f>
         <v>400</v>
       </c>
-      <c r="N2" s="6">
-        <f>SUM(B2:M2)</f>
-        <v>3800</v>
+      <c r="N2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="O2" s="6">
+        <f>SUM(B2:N2)</f>
+        <v>4100</v>
       </c>
     </row>
     <row r="3">
@@ -1212,9 +1223,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,M$1000)</f>
         <v>300</v>
       </c>
-      <c r="N3" s="6">
-        <f>SUM(B3:M3)</f>
-        <v>3250</v>
+      <c r="N3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="O3" s="6">
+        <f>SUM(B3:N3)</f>
+        <v>3650</v>
       </c>
     </row>
     <row r="4">
@@ -1270,8 +1285,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,M$1000)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="6">
-        <f>SUM(B4:M4)</f>
+      <c r="N4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <f>SUM(B4:N4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1328,9 +1347,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,M$1000)</f>
         <v>300</v>
       </c>
-      <c r="N5" s="6">
-        <f>SUM(B5:M5)</f>
-        <v>1950</v>
+      <c r="N5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="O5" s="6">
+        <f>SUM(B5:N5)</f>
+        <v>2250</v>
       </c>
     </row>
     <row r="6">
@@ -1386,8 +1409,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,M$1000)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="6">
-        <f>SUM(B6:M6)</f>
+      <c r="N6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <f>SUM(B6:N6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1444,9 +1471,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,M$1000)</f>
         <v>300</v>
       </c>
-      <c r="N7" s="6">
-        <f>SUM(B7:M7)</f>
-        <v>900</v>
+      <c r="N7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="O7" s="6">
+        <f>SUM(B7:N7)</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -1505,7 +1536,11 @@
       </c>
       <c r="N8" s="8">
         <f>SUM(N2:N7)</f>
-        <v>13800</v>
+        <v>1300</v>
+      </c>
+      <c r="O8" s="8">
+        <f>SUM(O2:O7)</f>
+        <v>15100</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1567,6 +1602,11 @@
       <c r="M1000" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="N1000" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5765,187 +5805,307 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n"/>
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B87" s="5" t="str">
         <f>IF(A87="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A87,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C87" s="5" t="str">
         <f>IF(A87="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A87,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H87" s="5" t="str">
         <f>IF(E87="","",IF(AND(F87="نعم",G87="نعم"),"جرد + مراجعة",IF(F87="نعم","جرد فقط",IF(G87="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I87" s="9">
         <f>IF(H87="جرد + مراجعة",الإعدادات!$B$2,IF(H87="مراجعة فقط",الإعدادات!$B$3,IF(H87="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n"/>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B88" s="5" t="str">
         <f>IF(A88="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A88,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C88" s="5" t="str">
         <f>IF(A88="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A88,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H88" s="5" t="str">
         <f>IF(E88="","",IF(AND(F88="نعم",G88="نعم"),"جرد + مراجعة",IF(F88="نعم","جرد فقط",IF(G88="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I88" s="9">
         <f>IF(H88="جرد + مراجعة",الإعدادات!$B$2,IF(H88="مراجعة فقط",الإعدادات!$B$3,IF(H88="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n"/>
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B89" s="5" t="str">
         <f>IF(A89="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A89,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C89" s="5" t="str">
         <f>IF(A89="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A89,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H89" s="5" t="str">
         <f>IF(E89="","",IF(AND(F89="نعم",G89="نعم"),"جرد + مراجعة",IF(F89="نعم","جرد فقط",IF(G89="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I89" s="9">
         <f>IF(H89="جرد + مراجعة",الإعدادات!$B$2,IF(H89="مراجعة فقط",الإعدادات!$B$3,IF(H89="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n"/>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B90" s="5" t="str">
         <f>IF(A90="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A90,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C90" s="5" t="str">
         <f>IF(A90="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A90,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H90" s="5" t="str">
         <f>IF(E90="","",IF(AND(F90="نعم",G90="نعم"),"جرد + مراجعة",IF(F90="نعم","جرد فقط",IF(G90="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I90" s="9">
         <f>IF(H90="جرد + مراجعة",الإعدادات!$B$2,IF(H90="مراجعة فقط",الإعدادات!$B$3,IF(H90="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n"/>
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B91" s="5" t="str">
         <f>IF(A91="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A91,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C91" s="5" t="str">
         <f>IF(A91="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A91,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H91" s="5" t="str">
         <f>IF(E91="","",IF(AND(F91="نعم",G91="نعم"),"جرد + مراجعة",IF(F91="نعم","جرد فقط",IF(G91="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I91" s="9">
         <f>IF(H91="جرد + مراجعة",الإعدادات!$B$2,IF(H91="مراجعة فقط",الإعدادات!$B$3,IF(H91="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n"/>
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B92" s="5" t="str">
         <f>IF(A92="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A92,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C92" s="5" t="str">
         <f>IF(A92="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A92,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H92" s="5" t="str">
         <f>IF(E92="","",IF(AND(F92="نعم",G92="نعم"),"جرد + مراجعة",IF(F92="نعم","جرد فقط",IF(G92="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I92" s="9">
         <f>IF(H92="جرد + مراجعة",الإعدادات!$B$2,IF(H92="مراجعة فقط",الإعدادات!$B$3,IF(H92="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n"/>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B93" s="5" t="str">
         <f>IF(A93="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A93,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C93" s="5" t="str">
         <f>IF(A93="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A93,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H93" s="5" t="str">
         <f>IF(E93="","",IF(AND(F93="نعم",G93="نعم"),"جرد + مراجعة",IF(F93="نعم","جرد فقط",IF(G93="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I93" s="9">
         <f>IF(H93="جرد + مراجعة",الإعدادات!$B$2,IF(H93="مراجعة فقط",الإعدادات!$B$3,IF(H93="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n"/>
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="B94" s="5" t="str">
         <f>IF(A94="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A94,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C94" s="5" t="str">
         <f>IF(A94="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A94,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="n"/>
-      <c r="F94" s="4" t="n"/>
-      <c r="G94" s="4" t="n"/>
+        <v>تمرة - الدواسر</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H94" s="5" t="str">
         <f>IF(E94="","",IF(AND(F94="نعم",G94="نعم"),"جرد + مراجعة",IF(F94="نعم","جرد فقط",IF(G94="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I94" s="9">
         <f>IF(H94="جرد + مراجعة",الإعدادات!$B$2,IF(H94="مراجعة فقط",الإعدادات!$B$3,IF(H94="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>4100</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>3650</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>2250</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>1200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>15100</v>
+        <v>16400</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>15100</v>
+        <v>16400</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:P1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1015,7 +1015,8 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1104,6 +1105,12 @@
       </c>
       <c r="O1" s="3" t="inlineStr">
         <is>
+          <t>الخميس
+2026-10-08</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1165,9 +1172,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,N$1000)</f>
         <v>300</v>
       </c>
-      <c r="O2" s="6">
-        <f>SUM(B2:N2)</f>
-        <v>4100</v>
+      <c r="O2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="P2" s="6">
+        <f>SUM(B2:O2)</f>
+        <v>4500</v>
       </c>
     </row>
     <row r="3">
@@ -1227,9 +1238,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,N$1000)</f>
         <v>400</v>
       </c>
-      <c r="O3" s="6">
-        <f>SUM(B3:N3)</f>
-        <v>3650</v>
+      <c r="O3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="P3" s="6">
+        <f>SUM(B3:O3)</f>
+        <v>3950</v>
       </c>
     </row>
     <row r="4">
@@ -1289,8 +1304,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,N$1000)</f>
         <v>0</v>
       </c>
-      <c r="O4" s="6">
-        <f>SUM(B4:N4)</f>
+      <c r="O4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>SUM(B4:O4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1351,9 +1370,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,N$1000)</f>
         <v>300</v>
       </c>
-      <c r="O5" s="6">
-        <f>SUM(B5:N5)</f>
-        <v>2250</v>
+      <c r="O5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="P5" s="6">
+        <f>SUM(B5:O5)</f>
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -1413,8 +1436,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,N$1000)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="6">
-        <f>SUM(B6:N6)</f>
+      <c r="O6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <f>SUM(B6:O6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1475,9 +1502,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,N$1000)</f>
         <v>300</v>
       </c>
-      <c r="O7" s="6">
-        <f>SUM(B7:N7)</f>
-        <v>1200</v>
+      <c r="O7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="P7" s="6">
+        <f>SUM(B7:O7)</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
@@ -1540,7 +1571,11 @@
       </c>
       <c r="O8" s="8">
         <f>SUM(O2:O7)</f>
-        <v>15100</v>
+        <v>1300</v>
+      </c>
+      <c r="P8" s="8">
+        <f>SUM(P2:P7)</f>
+        <v>16400</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1607,6 +1642,11 @@
       <c r="N1000" t="inlineStr">
         <is>
           <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="O1000" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6109,187 +6149,307 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n"/>
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B95" s="5" t="str">
         <f>IF(A95="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A95,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C95" s="5" t="str">
         <f>IF(A95="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A95,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H95" s="5" t="str">
         <f>IF(E95="","",IF(AND(F95="نعم",G95="نعم"),"جرد + مراجعة",IF(F95="نعم","جرد فقط",IF(G95="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I95" s="9">
         <f>IF(H95="جرد + مراجعة",الإعدادات!$B$2,IF(H95="مراجعة فقط",الإعدادات!$B$3,IF(H95="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n"/>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B96" s="5" t="str">
         <f>IF(A96="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A96,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C96" s="5" t="str">
         <f>IF(A96="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A96,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H96" s="5" t="str">
         <f>IF(E96="","",IF(AND(F96="نعم",G96="نعم"),"جرد + مراجعة",IF(F96="نعم","جرد فقط",IF(G96="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I96" s="9">
         <f>IF(H96="جرد + مراجعة",الإعدادات!$B$2,IF(H96="مراجعة فقط",الإعدادات!$B$3,IF(H96="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n"/>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B97" s="5" t="str">
         <f>IF(A97="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A97,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C97" s="5" t="str">
         <f>IF(A97="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A97,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H97" s="5" t="str">
         <f>IF(E97="","",IF(AND(F97="نعم",G97="نعم"),"جرد + مراجعة",IF(F97="نعم","جرد فقط",IF(G97="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I97" s="9">
         <f>IF(H97="جرد + مراجعة",الإعدادات!$B$2,IF(H97="مراجعة فقط",الإعدادات!$B$3,IF(H97="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n"/>
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B98" s="5" t="str">
         <f>IF(A98="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A98,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C98" s="5" t="str">
         <f>IF(A98="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A98,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H98" s="5" t="str">
         <f>IF(E98="","",IF(AND(F98="نعم",G98="نعم"),"جرد + مراجعة",IF(F98="نعم","جرد فقط",IF(G98="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I98" s="9">
         <f>IF(H98="جرد + مراجعة",الإعدادات!$B$2,IF(H98="مراجعة فقط",الإعدادات!$B$3,IF(H98="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n"/>
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B99" s="5" t="str">
         <f>IF(A99="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A99,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C99" s="5" t="str">
         <f>IF(A99="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A99,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H99" s="5" t="str">
         <f>IF(E99="","",IF(AND(F99="نعم",G99="نعم"),"جرد + مراجعة",IF(F99="نعم","جرد فقط",IF(G99="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I99" s="9">
         <f>IF(H99="جرد + مراجعة",الإعدادات!$B$2,IF(H99="مراجعة فقط",الإعدادات!$B$3,IF(H99="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n"/>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B100" s="5" t="str">
         <f>IF(A100="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A100,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C100" s="5" t="str">
         <f>IF(A100="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A100,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H100" s="5" t="str">
         <f>IF(E100="","",IF(AND(F100="نعم",G100="نعم"),"جرد + مراجعة",IF(F100="نعم","جرد فقط",IF(G100="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I100" s="9">
         <f>IF(H100="جرد + مراجعة",الإعدادات!$B$2,IF(H100="مراجعة فقط",الإعدادات!$B$3,IF(H100="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n"/>
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B101" s="5" t="str">
         <f>IF(A101="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A101,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C101" s="5" t="str">
         <f>IF(A101="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A101,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H101" s="5" t="str">
         <f>IF(E101="","",IF(AND(F101="نعم",G101="نعم"),"جرد + مراجعة",IF(F101="نعم","جرد فقط",IF(G101="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I101" s="9">
         <f>IF(H101="جرد + مراجعة",الإعدادات!$B$2,IF(H101="مراجعة فقط",الإعدادات!$B$3,IF(H101="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n"/>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="B102" s="5" t="str">
         <f>IF(A102="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A102,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C102" s="5" t="str">
         <f>IF(A102="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A102,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H102" s="5" t="str">
         <f>IF(E102="","",IF(AND(F102="نعم",G102="نعم"),"جرد + مراجعة",IF(F102="نعم","جرد فقط",IF(G102="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I102" s="9">
         <f>IF(H102="جرد + مراجعة",الإعدادات!$B$2,IF(H102="مراجعة فقط",الإعدادات!$B$3,IF(H102="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>4500</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>3950</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>2550</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>1500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>16400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>16400</v>
+        <v>17700</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1000"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1016,8 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1111,6 +1112,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
+          <t>الجمعة
+2026-10-09</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1176,9 +1183,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,O$1000)</f>
         <v>400</v>
       </c>
-      <c r="P2" s="6">
-        <f>SUM(B2:O2)</f>
-        <v>4500</v>
+      <c r="P2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="Q2" s="6">
+        <f>SUM(B2:P2)</f>
+        <v>4800</v>
       </c>
     </row>
     <row r="3">
@@ -1242,9 +1253,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,O$1000)</f>
         <v>300</v>
       </c>
-      <c r="P3" s="6">
-        <f>SUM(B3:O3)</f>
-        <v>3950</v>
+      <c r="P3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="Q3" s="6">
+        <f>SUM(B3:P3)</f>
+        <v>4350</v>
       </c>
     </row>
     <row r="4">
@@ -1308,8 +1323,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,O$1000)</f>
         <v>0</v>
       </c>
-      <c r="P4" s="6">
-        <f>SUM(B4:O4)</f>
+      <c r="P4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <f>SUM(B4:P4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1374,9 +1393,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,O$1000)</f>
         <v>300</v>
       </c>
-      <c r="P5" s="6">
-        <f>SUM(B5:O5)</f>
-        <v>2550</v>
+      <c r="P5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="Q5" s="6">
+        <f>SUM(B5:P5)</f>
+        <v>2850</v>
       </c>
     </row>
     <row r="6">
@@ -1440,8 +1463,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,O$1000)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="6">
-        <f>SUM(B6:O6)</f>
+      <c r="P6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <f>SUM(B6:P6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1506,9 +1533,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,O$1000)</f>
         <v>300</v>
       </c>
-      <c r="P7" s="6">
-        <f>SUM(B7:O7)</f>
-        <v>1500</v>
+      <c r="P7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="Q7" s="6">
+        <f>SUM(B7:P7)</f>
+        <v>1800</v>
       </c>
     </row>
     <row r="8">
@@ -1575,7 +1606,11 @@
       </c>
       <c r="P8" s="8">
         <f>SUM(P2:P7)</f>
-        <v>16400</v>
+        <v>1300</v>
+      </c>
+      <c r="Q8" s="8">
+        <f>SUM(Q2:Q7)</f>
+        <v>17700</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1647,6 +1682,11 @@
       <c r="O1000" t="inlineStr">
         <is>
           <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="P1000" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -6453,187 +6493,307 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n"/>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B103" s="5" t="str">
         <f>IF(A103="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A103,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C103" s="5" t="str">
         <f>IF(A103="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A103,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D103" s="4" t="n"/>
-      <c r="E103" s="4" t="n"/>
-      <c r="F103" s="4" t="n"/>
-      <c r="G103" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H103" s="5" t="str">
         <f>IF(E103="","",IF(AND(F103="نعم",G103="نعم"),"جرد + مراجعة",IF(F103="نعم","جرد فقط",IF(G103="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I103" s="9">
         <f>IF(H103="جرد + مراجعة",الإعدادات!$B$2,IF(H103="مراجعة فقط",الإعدادات!$B$3,IF(H103="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="n"/>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B104" s="5" t="str">
         <f>IF(A104="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A104,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C104" s="5" t="str">
         <f>IF(A104="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A104,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D104" s="4" t="n"/>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="4" t="n"/>
-      <c r="G104" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H104" s="5" t="str">
         <f>IF(E104="","",IF(AND(F104="نعم",G104="نعم"),"جرد + مراجعة",IF(F104="نعم","جرد فقط",IF(G104="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I104" s="9">
         <f>IF(H104="جرد + مراجعة",الإعدادات!$B$2,IF(H104="مراجعة فقط",الإعدادات!$B$3,IF(H104="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n"/>
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B105" s="5" t="str">
         <f>IF(A105="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A105,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C105" s="5" t="str">
         <f>IF(A105="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A105,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="n"/>
-      <c r="F105" s="4" t="n"/>
-      <c r="G105" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H105" s="5" t="str">
         <f>IF(E105="","",IF(AND(F105="نعم",G105="نعم"),"جرد + مراجعة",IF(F105="نعم","جرد فقط",IF(G105="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I105" s="9">
         <f>IF(H105="جرد + مراجعة",الإعدادات!$B$2,IF(H105="مراجعة فقط",الإعدادات!$B$3,IF(H105="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="n"/>
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B106" s="5" t="str">
         <f>IF(A106="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A106,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C106" s="5" t="str">
         <f>IF(A106="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A106,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H106" s="5" t="str">
         <f>IF(E106="","",IF(AND(F106="نعم",G106="نعم"),"جرد + مراجعة",IF(F106="نعم","جرد فقط",IF(G106="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I106" s="9">
         <f>IF(H106="جرد + مراجعة",الإعدادات!$B$2,IF(H106="مراجعة فقط",الإعدادات!$B$3,IF(H106="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n"/>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B107" s="5" t="str">
         <f>IF(A107="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A107,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C107" s="5" t="str">
         <f>IF(A107="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A107,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H107" s="5" t="str">
         <f>IF(E107="","",IF(AND(F107="نعم",G107="نعم"),"جرد + مراجعة",IF(F107="نعم","جرد فقط",IF(G107="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I107" s="9">
         <f>IF(H107="جرد + مراجعة",الإعدادات!$B$2,IF(H107="مراجعة فقط",الإعدادات!$B$3,IF(H107="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n"/>
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B108" s="5" t="str">
         <f>IF(A108="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A108,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C108" s="5" t="str">
         <f>IF(A108="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A108,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H108" s="5" t="str">
         <f>IF(E108="","",IF(AND(F108="نعم",G108="نعم"),"جرد + مراجعة",IF(F108="نعم","جرد فقط",IF(G108="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I108" s="9">
         <f>IF(H108="جرد + مراجعة",الإعدادات!$B$2,IF(H108="مراجعة فقط",الإعدادات!$B$3,IF(H108="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n"/>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B109" s="5" t="str">
         <f>IF(A109="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A109,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C109" s="5" t="str">
         <f>IF(A109="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A109,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="4" t="n"/>
-      <c r="G109" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H109" s="5" t="str">
         <f>IF(E109="","",IF(AND(F109="نعم",G109="نعم"),"جرد + مراجعة",IF(F109="نعم","جرد فقط",IF(G109="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I109" s="9">
         <f>IF(H109="جرد + مراجعة",الإعدادات!$B$2,IF(H109="مراجعة فقط",الإعدادات!$B$3,IF(H109="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="n"/>
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="B110" s="5" t="str">
         <f>IF(A110="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A110,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C110" s="5" t="str">
         <f>IF(A110="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A110,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H110" s="5" t="str">
         <f>IF(E110="","",IF(AND(F110="نعم",G110="نعم"),"جرد + مراجعة",IF(F110="نعم","جرد فقط",IF(G110="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I110" s="9">
         <f>IF(H110="جرد + مراجعة",الإعدادات!$B$2,IF(H110="مراجعة فقط",الإعدادات!$B$3,IF(H110="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>4800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>4350</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>2850</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>1800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>17700</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>17700</v>
+        <v>19000</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:R1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1017,7 +1017,8 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1118,6 +1119,12 @@
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
+          <t>السبت
+2026-10-10</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1187,9 +1194,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,P$1000)</f>
         <v>300</v>
       </c>
-      <c r="Q2" s="6">
-        <f>SUM(B2:P2)</f>
-        <v>4800</v>
+      <c r="Q2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="R2" s="6">
+        <f>SUM(B2:Q2)</f>
+        <v>5200</v>
       </c>
     </row>
     <row r="3">
@@ -1257,9 +1268,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,P$1000)</f>
         <v>400</v>
       </c>
-      <c r="Q3" s="6">
-        <f>SUM(B3:P3)</f>
-        <v>4350</v>
+      <c r="Q3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="R3" s="6">
+        <f>SUM(B3:Q3)</f>
+        <v>4650</v>
       </c>
     </row>
     <row r="4">
@@ -1327,8 +1342,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,P$1000)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="6">
-        <f>SUM(B4:P4)</f>
+      <c r="Q4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <f>SUM(B4:Q4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1397,9 +1416,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,P$1000)</f>
         <v>300</v>
       </c>
-      <c r="Q5" s="6">
-        <f>SUM(B5:P5)</f>
-        <v>2850</v>
+      <c r="Q5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="R5" s="6">
+        <f>SUM(B5:Q5)</f>
+        <v>3150</v>
       </c>
     </row>
     <row r="6">
@@ -1467,8 +1490,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,P$1000)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="6">
-        <f>SUM(B6:P6)</f>
+      <c r="Q6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <f>SUM(B6:Q6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1537,9 +1564,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,P$1000)</f>
         <v>300</v>
       </c>
-      <c r="Q7" s="6">
-        <f>SUM(B7:P7)</f>
-        <v>1800</v>
+      <c r="Q7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="R7" s="6">
+        <f>SUM(B7:Q7)</f>
+        <v>2100</v>
       </c>
     </row>
     <row r="8">
@@ -1610,7 +1641,11 @@
       </c>
       <c r="Q8" s="8">
         <f>SUM(Q2:Q7)</f>
-        <v>17700</v>
+        <v>1300</v>
+      </c>
+      <c r="R8" s="8">
+        <f>SUM(R2:R7)</f>
+        <v>19000</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1687,6 +1722,11 @@
       <c r="P1000" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Q1000" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6797,187 +6837,307 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n"/>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B111" s="5" t="str">
         <f>IF(A111="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A111,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C111" s="5" t="str">
         <f>IF(A111="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A111,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D111" s="4" t="n"/>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="n"/>
-      <c r="G111" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H111" s="5" t="str">
         <f>IF(E111="","",IF(AND(F111="نعم",G111="نعم"),"جرد + مراجعة",IF(F111="نعم","جرد فقط",IF(G111="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I111" s="9">
         <f>IF(H111="جرد + مراجعة",الإعدادات!$B$2,IF(H111="مراجعة فقط",الإعدادات!$B$3,IF(H111="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="n"/>
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B112" s="5" t="str">
         <f>IF(A112="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A112,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C112" s="5" t="str">
         <f>IF(A112="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A112,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H112" s="5" t="str">
         <f>IF(E112="","",IF(AND(F112="نعم",G112="نعم"),"جرد + مراجعة",IF(F112="نعم","جرد فقط",IF(G112="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I112" s="9">
         <f>IF(H112="جرد + مراجعة",الإعدادات!$B$2,IF(H112="مراجعة فقط",الإعدادات!$B$3,IF(H112="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n"/>
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B113" s="5" t="str">
         <f>IF(A113="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A113,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C113" s="5" t="str">
         <f>IF(A113="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A113,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H113" s="5" t="str">
         <f>IF(E113="","",IF(AND(F113="نعم",G113="نعم"),"جرد + مراجعة",IF(F113="نعم","جرد فقط",IF(G113="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I113" s="9">
         <f>IF(H113="جرد + مراجعة",الإعدادات!$B$2,IF(H113="مراجعة فقط",الإعدادات!$B$3,IF(H113="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="n"/>
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B114" s="5" t="str">
         <f>IF(A114="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A114,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C114" s="5" t="str">
         <f>IF(A114="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A114,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H114" s="5" t="str">
         <f>IF(E114="","",IF(AND(F114="نعم",G114="نعم"),"جرد + مراجعة",IF(F114="نعم","جرد فقط",IF(G114="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I114" s="9">
         <f>IF(H114="جرد + مراجعة",الإعدادات!$B$2,IF(H114="مراجعة فقط",الإعدادات!$B$3,IF(H114="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n"/>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B115" s="5" t="str">
         <f>IF(A115="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A115,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C115" s="5" t="str">
         <f>IF(A115="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A115,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D115" s="4" t="n"/>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="n"/>
-      <c r="G115" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H115" s="5" t="str">
         <f>IF(E115="","",IF(AND(F115="نعم",G115="نعم"),"جرد + مراجعة",IF(F115="نعم","جرد فقط",IF(G115="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I115" s="9">
         <f>IF(H115="جرد + مراجعة",الإعدادات!$B$2,IF(H115="مراجعة فقط",الإعدادات!$B$3,IF(H115="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="n"/>
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B116" s="5" t="str">
         <f>IF(A116="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A116,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C116" s="5" t="str">
         <f>IF(A116="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A116,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D116" s="4" t="n"/>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H116" s="5" t="str">
         <f>IF(E116="","",IF(AND(F116="نعم",G116="نعم"),"جرد + مراجعة",IF(F116="نعم","جرد فقط",IF(G116="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I116" s="9">
         <f>IF(H116="جرد + مراجعة",الإعدادات!$B$2,IF(H116="مراجعة فقط",الإعدادات!$B$3,IF(H116="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n"/>
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B117" s="5" t="str">
         <f>IF(A117="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A117,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C117" s="5" t="str">
         <f>IF(A117="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A117,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D117" s="4" t="n"/>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H117" s="5" t="str">
         <f>IF(E117="","",IF(AND(F117="نعم",G117="نعم"),"جرد + مراجعة",IF(F117="نعم","جرد فقط",IF(G117="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I117" s="9">
         <f>IF(H117="جرد + مراجعة",الإعدادات!$B$2,IF(H117="مراجعة فقط",الإعدادات!$B$3,IF(H117="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="n"/>
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
       <c r="B118" s="5" t="str">
         <f>IF(A118="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A118,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C118" s="5" t="str">
         <f>IF(A118="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A118,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="4" t="n"/>
+        <v>الدواسر</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H118" s="5" t="str">
         <f>IF(E118="","",IF(AND(F118="نعم",G118="نعم"),"جرد + مراجعة",IF(F118="نعم","جرد فقط",IF(G118="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I118" s="9">
         <f>IF(H118="جرد + مراجعة",الإعدادات!$B$2,IF(H118="مراجعة فقط",الإعدادات!$B$3,IF(H118="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="119">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>5200</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>4650</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>3150</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>2100</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>19000</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>19000</v>
+        <v>20300</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:S1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,8 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1125,6 +1126,12 @@
       </c>
       <c r="R1" s="3" t="inlineStr">
         <is>
+          <t>الأحد
+2026-10-11</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1198,9 +1205,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,Q$1000)</f>
         <v>400</v>
       </c>
-      <c r="R2" s="6">
-        <f>SUM(B2:Q2)</f>
-        <v>5200</v>
+      <c r="R2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="S2" s="6">
+        <f>SUM(B2:R2)</f>
+        <v>5500</v>
       </c>
     </row>
     <row r="3">
@@ -1272,9 +1283,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,Q$1000)</f>
         <v>300</v>
       </c>
-      <c r="R3" s="6">
-        <f>SUM(B3:Q3)</f>
-        <v>4650</v>
+      <c r="R3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="S3" s="6">
+        <f>SUM(B3:R3)</f>
+        <v>5050</v>
       </c>
     </row>
     <row r="4">
@@ -1346,8 +1361,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,Q$1000)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="6">
-        <f>SUM(B4:Q4)</f>
+      <c r="R4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <f>SUM(B4:R4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1420,9 +1439,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,Q$1000)</f>
         <v>300</v>
       </c>
-      <c r="R5" s="6">
-        <f>SUM(B5:Q5)</f>
-        <v>3150</v>
+      <c r="R5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="S5" s="6">
+        <f>SUM(B5:R5)</f>
+        <v>3450</v>
       </c>
     </row>
     <row r="6">
@@ -1494,8 +1517,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,Q$1000)</f>
         <v>0</v>
       </c>
-      <c r="R6" s="6">
-        <f>SUM(B6:Q6)</f>
+      <c r="R6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <f>SUM(B6:R6)</f>
         <v>2250</v>
       </c>
     </row>
@@ -1568,9 +1595,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,Q$1000)</f>
         <v>300</v>
       </c>
-      <c r="R7" s="6">
-        <f>SUM(B7:Q7)</f>
-        <v>2100</v>
+      <c r="R7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="S7" s="6">
+        <f>SUM(B7:R7)</f>
+        <v>2400</v>
       </c>
     </row>
     <row r="8">
@@ -1645,7 +1676,11 @@
       </c>
       <c r="R8" s="8">
         <f>SUM(R2:R7)</f>
-        <v>19000</v>
+        <v>1300</v>
+      </c>
+      <c r="S8" s="8">
+        <f>SUM(S2:S7)</f>
+        <v>20300</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1727,6 +1762,11 @@
       <c r="Q1000" t="inlineStr">
         <is>
           <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="R1000" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7141,187 +7181,307 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n"/>
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B119" s="5" t="str">
         <f>IF(A119="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A119,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C119" s="5" t="str">
         <f>IF(A119="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A119,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H119" s="5" t="str">
         <f>IF(E119="","",IF(AND(F119="نعم",G119="نعم"),"جرد + مراجعة",IF(F119="نعم","جرد فقط",IF(G119="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I119" s="9">
         <f>IF(H119="جرد + مراجعة",الإعدادات!$B$2,IF(H119="مراجعة فقط",الإعدادات!$B$3,IF(H119="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="n"/>
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B120" s="5" t="str">
         <f>IF(A120="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A120,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C120" s="5" t="str">
         <f>IF(A120="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A120,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H120" s="5" t="str">
         <f>IF(E120="","",IF(AND(F120="نعم",G120="نعم"),"جرد + مراجعة",IF(F120="نعم","جرد فقط",IF(G120="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I120" s="9">
         <f>IF(H120="جرد + مراجعة",الإعدادات!$B$2,IF(H120="مراجعة فقط",الإعدادات!$B$3,IF(H120="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n"/>
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B121" s="5" t="str">
         <f>IF(A121="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A121,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C121" s="5" t="str">
         <f>IF(A121="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A121,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D121" s="4" t="n"/>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H121" s="5" t="str">
         <f>IF(E121="","",IF(AND(F121="نعم",G121="نعم"),"جرد + مراجعة",IF(F121="نعم","جرد فقط",IF(G121="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I121" s="9">
         <f>IF(H121="جرد + مراجعة",الإعدادات!$B$2,IF(H121="مراجعة فقط",الإعدادات!$B$3,IF(H121="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="n"/>
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B122" s="5" t="str">
         <f>IF(A122="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A122,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C122" s="5" t="str">
         <f>IF(A122="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A122,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr"/>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H122" s="5" t="str">
         <f>IF(E122="","",IF(AND(F122="نعم",G122="نعم"),"جرد + مراجعة",IF(F122="نعم","جرد فقط",IF(G122="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I122" s="9">
         <f>IF(H122="جرد + مراجعة",الإعدادات!$B$2,IF(H122="مراجعة فقط",الإعدادات!$B$3,IF(H122="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="n"/>
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B123" s="5" t="str">
         <f>IF(A123="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A123,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C123" s="5" t="str">
         <f>IF(A123="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A123,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D123" s="4" t="n"/>
-      <c r="E123" s="4" t="n"/>
-      <c r="F123" s="4" t="n"/>
-      <c r="G123" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H123" s="5" t="str">
         <f>IF(E123="","",IF(AND(F123="نعم",G123="نعم"),"جرد + مراجعة",IF(F123="نعم","جرد فقط",IF(G123="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I123" s="9">
         <f>IF(H123="جرد + مراجعة",الإعدادات!$B$2,IF(H123="مراجعة فقط",الإعدادات!$B$3,IF(H123="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="n"/>
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B124" s="5" t="str">
         <f>IF(A124="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A124,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C124" s="5" t="str">
         <f>IF(A124="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A124,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D124" s="4" t="n"/>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H124" s="5" t="str">
         <f>IF(E124="","",IF(AND(F124="نعم",G124="نعم"),"جرد + مراجعة",IF(F124="نعم","جرد فقط",IF(G124="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I124" s="9">
         <f>IF(H124="جرد + مراجعة",الإعدادات!$B$2,IF(H124="مراجعة فقط",الإعدادات!$B$3,IF(H124="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="n"/>
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B125" s="5" t="str">
         <f>IF(A125="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A125,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C125" s="5" t="str">
         <f>IF(A125="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A125,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D125" s="4" t="n"/>
-      <c r="E125" s="4" t="n"/>
-      <c r="F125" s="4" t="n"/>
-      <c r="G125" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr"/>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H125" s="5" t="str">
         <f>IF(E125="","",IF(AND(F125="نعم",G125="نعم"),"جرد + مراجعة",IF(F125="نعم","جرد فقط",IF(G125="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I125" s="9">
         <f>IF(H125="جرد + مراجعة",الإعدادات!$B$2,IF(H125="مراجعة فقط",الإعدادات!$B$3,IF(H125="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="n"/>
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="B126" s="5" t="str">
         <f>IF(A126="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A126,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C126" s="5" t="str">
         <f>IF(A126="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A126,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D126" s="4" t="n"/>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="4" t="n"/>
-      <c r="G126" s="4" t="n"/>
+        <v>رنية</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H126" s="5" t="str">
         <f>IF(E126="","",IF(AND(F126="نعم",G126="نعم"),"جرد + مراجعة",IF(F126="نعم","جرد فقط",IF(G126="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I126" s="9">
         <f>IF(H126="جرد + مراجعة",الإعدادات!$B$2,IF(H126="مراجعة فقط",الإعدادات!$B$3,IF(H126="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="127">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>5500</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>5050</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>2250</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="9">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>2400</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="10">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>20300</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>20300</v>
+        <v>21600</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1019,7 +1019,8 @@
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1132,6 +1133,12 @@
       </c>
       <c r="S1" s="3" t="inlineStr">
         <is>
+          <t>الثلاثاء
+2026-10-13</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1209,9 +1216,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,R$1000)</f>
         <v>300</v>
       </c>
-      <c r="S2" s="6">
-        <f>SUM(B2:R2)</f>
-        <v>5500</v>
+      <c r="S2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="T2" s="6">
+        <f>SUM(B2:S2)</f>
+        <v>5800</v>
       </c>
     </row>
     <row r="3">
@@ -1287,9 +1298,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,R$1000)</f>
         <v>400</v>
       </c>
-      <c r="S3" s="6">
-        <f>SUM(B3:R3)</f>
-        <v>5050</v>
+      <c r="S3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="T3" s="6">
+        <f>SUM(B3:S3)</f>
+        <v>5350</v>
       </c>
     </row>
     <row r="4">
@@ -1365,8 +1380,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,R$1000)</f>
         <v>0</v>
       </c>
-      <c r="S4" s="6">
-        <f>SUM(B4:R4)</f>
+      <c r="S4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="6">
+        <f>SUM(B4:S4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1443,8 +1462,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,R$1000)</f>
         <v>300</v>
       </c>
-      <c r="S5" s="6">
-        <f>SUM(B5:R5)</f>
+      <c r="S5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="6">
+        <f>SUM(B5:S5)</f>
         <v>3450</v>
       </c>
     </row>
@@ -1521,9 +1544,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,R$1000)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="6">
-        <f>SUM(B6:R6)</f>
-        <v>2250</v>
+      <c r="S6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="T6" s="6">
+        <f>SUM(B6:S6)</f>
+        <v>2650</v>
       </c>
     </row>
     <row r="7">
@@ -1599,9 +1626,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,R$1000)</f>
         <v>300</v>
       </c>
-      <c r="S7" s="6">
-        <f>SUM(B7:R7)</f>
-        <v>2400</v>
+      <c r="S7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="T7" s="6">
+        <f>SUM(B7:S7)</f>
+        <v>2700</v>
       </c>
     </row>
     <row r="8">
@@ -1680,7 +1711,11 @@
       </c>
       <c r="S8" s="8">
         <f>SUM(S2:S7)</f>
-        <v>20300</v>
+        <v>1300</v>
+      </c>
+      <c r="T8" s="8">
+        <f>SUM(T2:T7)</f>
+        <v>21600</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1767,6 +1802,11 @@
       <c r="R1000" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="S1000" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7485,187 +7525,307 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="n"/>
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B127" s="5" t="str">
         <f>IF(A127="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A127,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C127" s="5" t="str">
         <f>IF(A127="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A127,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D127" s="4" t="n"/>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="n"/>
-      <c r="G127" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H127" s="5" t="str">
         <f>IF(E127="","",IF(AND(F127="نعم",G127="نعم"),"جرد + مراجعة",IF(F127="نعم","جرد فقط",IF(G127="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I127" s="9">
         <f>IF(H127="جرد + مراجعة",الإعدادات!$B$2,IF(H127="مراجعة فقط",الإعدادات!$B$3,IF(H127="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="n"/>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B128" s="5" t="str">
         <f>IF(A128="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A128,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C128" s="5" t="str">
         <f>IF(A128="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A128,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="4" t="n"/>
-      <c r="G128" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H128" s="5" t="str">
         <f>IF(E128="","",IF(AND(F128="نعم",G128="نعم"),"جرد + مراجعة",IF(F128="نعم","جرد فقط",IF(G128="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I128" s="9">
         <f>IF(H128="جرد + مراجعة",الإعدادات!$B$2,IF(H128="مراجعة فقط",الإعدادات!$B$3,IF(H128="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="n"/>
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B129" s="5" t="str">
         <f>IF(A129="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A129,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C129" s="5" t="str">
         <f>IF(A129="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A129,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D129" s="4" t="n"/>
-      <c r="E129" s="4" t="n"/>
-      <c r="F129" s="4" t="n"/>
-      <c r="G129" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H129" s="5" t="str">
         <f>IF(E129="","",IF(AND(F129="نعم",G129="نعم"),"جرد + مراجعة",IF(F129="نعم","جرد فقط",IF(G129="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I129" s="9">
         <f>IF(H129="جرد + مراجعة",الإعدادات!$B$2,IF(H129="مراجعة فقط",الإعدادات!$B$3,IF(H129="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="n"/>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B130" s="5" t="str">
         <f>IF(A130="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A130,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C130" s="5" t="str">
         <f>IF(A130="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A130,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D130" s="4" t="n"/>
-      <c r="E130" s="4" t="n"/>
-      <c r="F130" s="4" t="n"/>
-      <c r="G130" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H130" s="5" t="str">
         <f>IF(E130="","",IF(AND(F130="نعم",G130="نعم"),"جرد + مراجعة",IF(F130="نعم","جرد فقط",IF(G130="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I130" s="9">
         <f>IF(H130="جرد + مراجعة",الإعدادات!$B$2,IF(H130="مراجعة فقط",الإعدادات!$B$3,IF(H130="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="n"/>
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B131" s="5" t="str">
         <f>IF(A131="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A131,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C131" s="5" t="str">
         <f>IF(A131="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A131,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D131" s="4" t="n"/>
-      <c r="E131" s="4" t="n"/>
-      <c r="F131" s="4" t="n"/>
-      <c r="G131" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H131" s="5" t="str">
         <f>IF(E131="","",IF(AND(F131="نعم",G131="نعم"),"جرد + مراجعة",IF(F131="نعم","جرد فقط",IF(G131="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I131" s="9">
         <f>IF(H131="جرد + مراجعة",الإعدادات!$B$2,IF(H131="مراجعة فقط",الإعدادات!$B$3,IF(H131="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="n"/>
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B132" s="5" t="str">
         <f>IF(A132="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A132,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C132" s="5" t="str">
         <f>IF(A132="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A132,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D132" s="4" t="n"/>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="n"/>
-      <c r="G132" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr"/>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H132" s="5" t="str">
         <f>IF(E132="","",IF(AND(F132="نعم",G132="نعم"),"جرد + مراجعة",IF(F132="نعم","جرد فقط",IF(G132="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I132" s="9">
         <f>IF(H132="جرد + مراجعة",الإعدادات!$B$2,IF(H132="مراجعة فقط",الإعدادات!$B$3,IF(H132="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="n"/>
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B133" s="5" t="str">
         <f>IF(A133="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A133,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C133" s="5" t="str">
         <f>IF(A133="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A133,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D133" s="4" t="n"/>
-      <c r="E133" s="4" t="n"/>
-      <c r="F133" s="4" t="n"/>
-      <c r="G133" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد جمال</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr"/>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H133" s="5" t="str">
         <f>IF(E133="","",IF(AND(F133="نعم",G133="نعم"),"جرد + مراجعة",IF(F133="نعم","جرد فقط",IF(G133="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I133" s="9">
         <f>IF(H133="جرد + مراجعة",الإعدادات!$B$2,IF(H133="مراجعة فقط",الإعدادات!$B$3,IF(H133="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="n"/>
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="B134" s="5" t="str">
         <f>IF(A134="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A134,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C134" s="5" t="str">
         <f>IF(A134="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A134,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D134" s="4" t="n"/>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H134" s="5" t="str">
         <f>IF(E134="","",IF(AND(F134="نعم",G134="نعم"),"جرد + مراجعة",IF(F134="نعم","جرد فقط",IF(G134="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I134" s="9">
         <f>IF(H134="جرد + مراجعة",الإعدادات!$B$2,IF(H134="مراجعة فقط",الإعدادات!$B$3,IF(H134="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="135">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>5800</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>5350</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>2650</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="9">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>21600</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>21600</v>
+        <v>22600</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1000"/>
+  <dimension ref="A1:U1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1020,7 +1020,8 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1139,6 +1140,12 @@
       </c>
       <c r="T1" s="3" t="inlineStr">
         <is>
+          <t>الأربعاء
+2026-10-14</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1220,9 +1227,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,S$1000)</f>
         <v>300</v>
       </c>
-      <c r="T2" s="6">
-        <f>SUM(B2:S2)</f>
-        <v>5800</v>
+      <c r="T2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="U2" s="6">
+        <f>SUM(B2:T2)</f>
+        <v>6200</v>
       </c>
     </row>
     <row r="3">
@@ -1302,9 +1313,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,S$1000)</f>
         <v>300</v>
       </c>
-      <c r="T3" s="6">
-        <f>SUM(B3:S3)</f>
-        <v>5350</v>
+      <c r="T3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="U3" s="6">
+        <f>SUM(B3:T3)</f>
+        <v>5650</v>
       </c>
     </row>
     <row r="4">
@@ -1384,8 +1399,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,S$1000)</f>
         <v>0</v>
       </c>
-      <c r="T4" s="6">
-        <f>SUM(B4:S4)</f>
+      <c r="T4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <f>SUM(B4:T4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1466,8 +1485,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,S$1000)</f>
         <v>0</v>
       </c>
-      <c r="T5" s="6">
-        <f>SUM(B5:S5)</f>
+      <c r="T5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
+        <f>SUM(B5:T5)</f>
         <v>3450</v>
       </c>
     </row>
@@ -1548,9 +1571,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,S$1000)</f>
         <v>400</v>
       </c>
-      <c r="T6" s="6">
-        <f>SUM(B6:S6)</f>
-        <v>2650</v>
+      <c r="T6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="U6" s="6">
+        <f>SUM(B6:T6)</f>
+        <v>2950</v>
       </c>
     </row>
     <row r="7">
@@ -1630,8 +1657,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,S$1000)</f>
         <v>300</v>
       </c>
-      <c r="T7" s="6">
-        <f>SUM(B7:S7)</f>
+      <c r="T7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="6">
+        <f>SUM(B7:T7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1715,7 +1746,11 @@
       </c>
       <c r="T8" s="8">
         <f>SUM(T2:T7)</f>
-        <v>21600</v>
+        <v>1000</v>
+      </c>
+      <c r="U8" s="8">
+        <f>SUM(U2:U7)</f>
+        <v>22600</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1807,6 +1842,11 @@
       <c r="S1000" t="inlineStr">
         <is>
           <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="T1000" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -7829,141 +7869,233 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="n"/>
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="B135" s="5" t="str">
         <f>IF(A135="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A135,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C135" s="5" t="str">
         <f>IF(A135="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A135,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D135" s="4" t="n"/>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="4" t="n"/>
-      <c r="G135" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H135" s="5" t="str">
         <f>IF(E135="","",IF(AND(F135="نعم",G135="نعم"),"جرد + مراجعة",IF(F135="نعم","جرد فقط",IF(G135="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I135" s="9">
         <f>IF(H135="جرد + مراجعة",الإعدادات!$B$2,IF(H135="مراجعة فقط",الإعدادات!$B$3,IF(H135="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="n"/>
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="B136" s="5" t="str">
         <f>IF(A136="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A136,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C136" s="5" t="str">
         <f>IF(A136="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A136,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr"/>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H136" s="5" t="str">
         <f>IF(E136="","",IF(AND(F136="نعم",G136="نعم"),"جرد + مراجعة",IF(F136="نعم","جرد فقط",IF(G136="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I136" s="9">
         <f>IF(H136="جرد + مراجعة",الإعدادات!$B$2,IF(H136="مراجعة فقط",الإعدادات!$B$3,IF(H136="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="n"/>
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="B137" s="5" t="str">
         <f>IF(A137="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A137,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C137" s="5" t="str">
         <f>IF(A137="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A137,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H137" s="5" t="str">
         <f>IF(E137="","",IF(AND(F137="نعم",G137="نعم"),"جرد + مراجعة",IF(F137="نعم","جرد فقط",IF(G137="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I137" s="9">
         <f>IF(H137="جرد + مراجعة",الإعدادات!$B$2,IF(H137="مراجعة فقط",الإعدادات!$B$3,IF(H137="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="n"/>
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="B138" s="5" t="str">
         <f>IF(A138="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A138,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C138" s="5" t="str">
         <f>IF(A138="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A138,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D138" s="4" t="n"/>
-      <c r="E138" s="4" t="n"/>
-      <c r="F138" s="4" t="n"/>
-      <c r="G138" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H138" s="5" t="str">
         <f>IF(E138="","",IF(AND(F138="نعم",G138="نعم"),"جرد + مراجعة",IF(F138="نعم","جرد فقط",IF(G138="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I138" s="9">
         <f>IF(H138="جرد + مراجعة",الإعدادات!$B$2,IF(H138="مراجعة فقط",الإعدادات!$B$3,IF(H138="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="n"/>
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="B139" s="5" t="str">
         <f>IF(A139="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A139,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C139" s="5" t="str">
         <f>IF(A139="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A139,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D139" s="4" t="n"/>
-      <c r="E139" s="4" t="n"/>
-      <c r="F139" s="4" t="n"/>
-      <c r="G139" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H139" s="5" t="str">
         <f>IF(E139="","",IF(AND(F139="نعم",G139="نعم"),"جرد + مراجعة",IF(F139="نعم","جرد فقط",IF(G139="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I139" s="9">
         <f>IF(H139="جرد + مراجعة",الإعدادات!$B$2,IF(H139="مراجعة فقط",الإعدادات!$B$3,IF(H139="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="n"/>
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="B140" s="5" t="str">
         <f>IF(A140="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A140,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C140" s="5" t="str">
         <f>IF(A140="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A140,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D140" s="4" t="n"/>
-      <c r="E140" s="4" t="n"/>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H140" s="5" t="str">
         <f>IF(E140="","",IF(AND(F140="نعم",G140="نعم"),"جرد + مراجعة",IF(F140="نعم","جرد فقط",IF(G140="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I140" s="9">
         <f>IF(H140="جرد + مراجعة",الإعدادات!$B$2,IF(H140="مراجعة فقط",الإعدادات!$B$3,IF(H140="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="141">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>6200</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>5650</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>2950</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="9">
@@ -957,11 +957,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +969,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>22600</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>22600</v>
+        <v>23600</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1000"/>
+  <dimension ref="A1:V1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1021,7 +1021,8 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1146,6 +1147,12 @@
       </c>
       <c r="U1" s="3" t="inlineStr">
         <is>
+          <t>الخميس
+2026-10-15</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1231,9 +1238,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,T$1000)</f>
         <v>400</v>
       </c>
-      <c r="U2" s="6">
-        <f>SUM(B2:T2)</f>
-        <v>6200</v>
+      <c r="U2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="V2" s="6">
+        <f>SUM(B2:U2)</f>
+        <v>6500</v>
       </c>
     </row>
     <row r="3">
@@ -1317,9 +1328,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,T$1000)</f>
         <v>300</v>
       </c>
-      <c r="U3" s="6">
-        <f>SUM(B3:T3)</f>
-        <v>5650</v>
+      <c r="U3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="V3" s="6">
+        <f>SUM(B3:U3)</f>
+        <v>5950</v>
       </c>
     </row>
     <row r="4">
@@ -1403,8 +1418,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,T$1000)</f>
         <v>0</v>
       </c>
-      <c r="U4" s="6">
-        <f>SUM(B4:T4)</f>
+      <c r="U4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="6">
+        <f>SUM(B4:U4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1489,8 +1508,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,T$1000)</f>
         <v>0</v>
       </c>
-      <c r="U5" s="6">
-        <f>SUM(B5:T5)</f>
+      <c r="U5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="6">
+        <f>SUM(B5:U5)</f>
         <v>3450</v>
       </c>
     </row>
@@ -1575,9 +1598,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,T$1000)</f>
         <v>300</v>
       </c>
-      <c r="U6" s="6">
-        <f>SUM(B6:T6)</f>
-        <v>2950</v>
+      <c r="U6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="V6" s="6">
+        <f>SUM(B6:U6)</f>
+        <v>3350</v>
       </c>
     </row>
     <row r="7">
@@ -1661,8 +1688,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,T$1000)</f>
         <v>0</v>
       </c>
-      <c r="U7" s="6">
-        <f>SUM(B7:T7)</f>
+      <c r="U7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="6">
+        <f>SUM(B7:U7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1750,7 +1781,11 @@
       </c>
       <c r="U8" s="8">
         <f>SUM(U2:U7)</f>
-        <v>22600</v>
+        <v>1000</v>
+      </c>
+      <c r="V8" s="8">
+        <f>SUM(V2:V7)</f>
+        <v>23600</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1847,6 +1882,11 @@
       <c r="T1000" t="inlineStr">
         <is>
           <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U1000" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8099,141 +8139,233 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="n"/>
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="B141" s="5" t="str">
         <f>IF(A141="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A141,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C141" s="5" t="str">
         <f>IF(A141="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A141,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H141" s="5" t="str">
         <f>IF(E141="","",IF(AND(F141="نعم",G141="نعم"),"جرد + مراجعة",IF(F141="نعم","جرد فقط",IF(G141="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I141" s="9">
         <f>IF(H141="جرد + مراجعة",الإعدادات!$B$2,IF(H141="مراجعة فقط",الإعدادات!$B$3,IF(H141="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="n"/>
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="B142" s="5" t="str">
         <f>IF(A142="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A142,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C142" s="5" t="str">
         <f>IF(A142="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A142,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="n"/>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr"/>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H142" s="5" t="str">
         <f>IF(E142="","",IF(AND(F142="نعم",G142="نعم"),"جرد + مراجعة",IF(F142="نعم","جرد فقط",IF(G142="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I142" s="9">
         <f>IF(H142="جرد + مراجعة",الإعدادات!$B$2,IF(H142="مراجعة فقط",الإعدادات!$B$3,IF(H142="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="n"/>
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="B143" s="5" t="str">
         <f>IF(A143="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A143,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C143" s="5" t="str">
         <f>IF(A143="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A143,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr"/>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H143" s="5" t="str">
         <f>IF(E143="","",IF(AND(F143="نعم",G143="نعم"),"جرد + مراجعة",IF(F143="نعم","جرد فقط",IF(G143="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I143" s="9">
         <f>IF(H143="جرد + مراجعة",الإعدادات!$B$2,IF(H143="مراجعة فقط",الإعدادات!$B$3,IF(H143="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="n"/>
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="B144" s="5" t="str">
         <f>IF(A144="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A144,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C144" s="5" t="str">
         <f>IF(A144="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A144,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="n"/>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H144" s="5" t="str">
         <f>IF(E144="","",IF(AND(F144="نعم",G144="نعم"),"جرد + مراجعة",IF(F144="نعم","جرد فقط",IF(G144="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I144" s="9">
         <f>IF(H144="جرد + مراجعة",الإعدادات!$B$2,IF(H144="مراجعة فقط",الإعدادات!$B$3,IF(H144="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="n"/>
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="B145" s="5" t="str">
         <f>IF(A145="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A145,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C145" s="5" t="str">
         <f>IF(A145="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A145,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D145" s="4" t="n"/>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H145" s="5" t="str">
         <f>IF(E145="","",IF(AND(F145="نعم",G145="نعم"),"جرد + مراجعة",IF(F145="نعم","جرد فقط",IF(G145="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I145" s="9">
         <f>IF(H145="جرد + مراجعة",الإعدادات!$B$2,IF(H145="مراجعة فقط",الإعدادات!$B$3,IF(H145="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="n"/>
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="B146" s="5" t="str">
         <f>IF(A146="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A146,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C146" s="5" t="str">
         <f>IF(A146="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A146,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D146" s="4" t="n"/>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="4" t="n"/>
-      <c r="G146" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr"/>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H146" s="5" t="str">
         <f>IF(E146="","",IF(AND(F146="نعم",G146="نعم"),"جرد + مراجعة",IF(F146="نعم","جرد فقط",IF(G146="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I146" s="9">
         <f>IF(H146="جرد + مراجعة",الإعدادات!$B$2,IF(H146="مراجعة فقط",الإعدادات!$B$3,IF(H146="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="147">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>6500</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="5">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5">
         <f>IF(A7="","",COUNTIFS(السجل!$E$2:$E$1000,A7,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -681,11 +681,11 @@
       </c>
       <c r="E7" s="5">
         <f>IF(A7="","",SUM(B7:D7))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="6">
         <f>IF(A7="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A7))</f>
-        <v>3450</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>3350</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="9">
@@ -743,26 +743,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="5" t="str">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد فؤاد</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
         <f>IF(A10="","",COUNTIFS(السجل!$E$2:$E$1000,A10,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
         <f>IF(A10="","",COUNTIFS(السجل!$E$2:$E$1000,A10,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v/>
-      </c>
-      <c r="D10" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
         <f>IF(A10="","",COUNTIFS(السجل!$E$2:$E$1000,A10,السجل!$H$2:$H$1000,"جرد فقط"))</f>
-        <v/>
-      </c>
-      <c r="E10" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
         <f>IF(A10="","",SUM(B10:D10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="str">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
         <f>IF(A10="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A10))</f>
-        <v/>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -957,11 +961,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -969,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>23600</v>
+        <v>24250</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>23600</v>
+        <v>24250</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1000"/>
+  <dimension ref="A1:W1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1022,7 +1026,8 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1153,6 +1158,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>الجمعة
+2026-10-16</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1242,9 +1253,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,U$1000)</f>
         <v>300</v>
       </c>
-      <c r="V2" s="6">
-        <f>SUM(B2:U2)</f>
-        <v>6500</v>
+      <c r="V2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>200</v>
+      </c>
+      <c r="W2" s="6">
+        <f>SUM(B2:V2)</f>
+        <v>6700</v>
       </c>
     </row>
     <row r="3">
@@ -1332,8 +1347,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,U$1000)</f>
         <v>300</v>
       </c>
-      <c r="V3" s="6">
-        <f>SUM(B3:U3)</f>
+      <c r="V3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="6">
+        <f>SUM(B3:V3)</f>
         <v>5950</v>
       </c>
     </row>
@@ -1422,8 +1441,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,U$1000)</f>
         <v>0</v>
       </c>
-      <c r="V4" s="6">
-        <f>SUM(B4:U4)</f>
+      <c r="V4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="6">
+        <f>SUM(B4:V4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1512,9 +1535,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,U$1000)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="6">
-        <f>SUM(B5:U5)</f>
-        <v>3450</v>
+      <c r="V5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="W5" s="6">
+        <f>SUM(B5:V5)</f>
+        <v>3600</v>
       </c>
     </row>
     <row r="6">
@@ -1602,9 +1629,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,U$1000)</f>
         <v>400</v>
       </c>
-      <c r="V6" s="6">
-        <f>SUM(B6:U6)</f>
-        <v>3350</v>
+      <c r="V6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="W6" s="6">
+        <f>SUM(B6:V6)</f>
+        <v>3500</v>
       </c>
     </row>
     <row r="7">
@@ -1692,100 +1723,202 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,U$1000)</f>
         <v>0</v>
       </c>
-      <c r="V7" s="6">
-        <f>SUM(B7:U7)</f>
+      <c r="V7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="6">
+        <f>SUM(B7:V7)</f>
         <v>2700</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="10" t="str">
+        <f>الملخص!A10</f>
+        <v>د. محمد فؤاد</v>
+      </c>
+      <c r="B8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,B$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,C$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,D$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,E$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,F$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,G$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,H$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,I$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,J$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,K$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,L$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,M$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,N$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,O$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,P$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,Q$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,R$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,S$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,T$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,U$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,V$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="W8" s="6">
+        <f>SUM(B8:V8)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B8" s="8">
-        <f>SUM(B2:B7)</f>
+      <c r="B9" s="8">
+        <f>SUM(B2:B8)</f>
         <v>1150</v>
       </c>
-      <c r="C8" s="8">
-        <f>SUM(C2:C7)</f>
+      <c r="C9" s="8">
+        <f>SUM(C2:C8)</f>
         <v>1000</v>
       </c>
-      <c r="D8" s="8">
-        <f>SUM(D2:D7)</f>
+      <c r="D9" s="8">
+        <f>SUM(D2:D8)</f>
         <v>1150</v>
       </c>
-      <c r="E8" s="8">
-        <f>SUM(E2:E7)</f>
+      <c r="E9" s="8">
+        <f>SUM(E2:E8)</f>
         <v>1150</v>
       </c>
-      <c r="F8" s="8">
-        <f>SUM(F2:F7)</f>
+      <c r="F9" s="8">
+        <f>SUM(F2:F8)</f>
         <v>1600</v>
       </c>
-      <c r="G8" s="8">
-        <f>SUM(G2:G7)</f>
+      <c r="G9" s="8">
+        <f>SUM(G2:G8)</f>
         <v>1450</v>
       </c>
-      <c r="H8" s="8">
-        <f>SUM(H2:H7)</f>
+      <c r="H9" s="8">
+        <f>SUM(H2:H8)</f>
         <v>800</v>
       </c>
-      <c r="I8" s="8">
-        <f>SUM(I2:I7)</f>
+      <c r="I9" s="8">
+        <f>SUM(I2:I8)</f>
         <v>800</v>
       </c>
-      <c r="J8" s="8">
-        <f>SUM(J2:J7)</f>
+      <c r="J9" s="8">
+        <f>SUM(J2:J8)</f>
         <v>800</v>
       </c>
-      <c r="K8" s="8">
-        <f>SUM(K2:K7)</f>
+      <c r="K9" s="8">
+        <f>SUM(K2:K8)</f>
         <v>1300</v>
       </c>
-      <c r="L8" s="8">
-        <f>SUM(L2:L7)</f>
+      <c r="L9" s="8">
+        <f>SUM(L2:L8)</f>
         <v>1300</v>
       </c>
-      <c r="M8" s="8">
-        <f>SUM(M2:M7)</f>
+      <c r="M9" s="8">
+        <f>SUM(M2:M8)</f>
         <v>1300</v>
       </c>
-      <c r="N8" s="8">
-        <f>SUM(N2:N7)</f>
+      <c r="N9" s="8">
+        <f>SUM(N2:N8)</f>
         <v>1300</v>
       </c>
-      <c r="O8" s="8">
-        <f>SUM(O2:O7)</f>
+      <c r="O9" s="8">
+        <f>SUM(O2:O8)</f>
         <v>1300</v>
       </c>
-      <c r="P8" s="8">
-        <f>SUM(P2:P7)</f>
+      <c r="P9" s="8">
+        <f>SUM(P2:P8)</f>
         <v>1300</v>
       </c>
-      <c r="Q8" s="8">
-        <f>SUM(Q2:Q7)</f>
+      <c r="Q9" s="8">
+        <f>SUM(Q2:Q8)</f>
         <v>1300</v>
       </c>
-      <c r="R8" s="8">
-        <f>SUM(R2:R7)</f>
+      <c r="R9" s="8">
+        <f>SUM(R2:R8)</f>
         <v>1300</v>
       </c>
-      <c r="S8" s="8">
-        <f>SUM(S2:S7)</f>
+      <c r="S9" s="8">
+        <f>SUM(S2:S8)</f>
         <v>1300</v>
       </c>
-      <c r="T8" s="8">
-        <f>SUM(T2:T7)</f>
+      <c r="T9" s="8">
+        <f>SUM(T2:T8)</f>
         <v>1000</v>
       </c>
-      <c r="U8" s="8">
-        <f>SUM(U2:U7)</f>
+      <c r="U9" s="8">
+        <f>SUM(U2:U8)</f>
         <v>1000</v>
       </c>
-      <c r="V8" s="8">
-        <f>SUM(V2:V7)</f>
-        <v>23600</v>
+      <c r="V9" s="8">
+        <f>SUM(V2:V8)</f>
+        <v>650</v>
+      </c>
+      <c r="W9" s="8">
+        <f>SUM(W2:W8)</f>
+        <v>24250</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -1887,6 +2020,11 @@
       <c r="U1000" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="V1000" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -8369,95 +8507,155 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="n"/>
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="B147" s="5" t="str">
         <f>IF(A147="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A147,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C147" s="5" t="str">
         <f>IF(A147="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A147,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D147" s="4" t="n"/>
-      <c r="E147" s="4" t="n"/>
-      <c r="F147" s="4" t="n"/>
-      <c r="G147" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H147" s="5" t="str">
         <f>IF(E147="","",IF(AND(F147="نعم",G147="نعم"),"جرد + مراجعة",IF(F147="نعم","جرد فقط",IF(G147="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I147" s="9">
         <f>IF(H147="جرد + مراجعة",الإعدادات!$B$2,IF(H147="مراجعة فقط",الإعدادات!$B$3,IF(H147="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="n"/>
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="B148" s="5" t="str">
         <f>IF(A148="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A148,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C148" s="5" t="str">
         <f>IF(A148="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A148,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D148" s="4" t="n"/>
-      <c r="E148" s="4" t="n"/>
-      <c r="F148" s="4" t="n"/>
-      <c r="G148" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr"/>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H148" s="5" t="str">
         <f>IF(E148="","",IF(AND(F148="نعم",G148="نعم"),"جرد + مراجعة",IF(F148="نعم","جرد فقط",IF(G148="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I148" s="9">
         <f>IF(H148="جرد + مراجعة",الإعدادات!$B$2,IF(H148="مراجعة فقط",الإعدادات!$B$3,IF(H148="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="n"/>
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="B149" s="5" t="str">
         <f>IF(A149="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A149,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C149" s="5" t="str">
         <f>IF(A149="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A149,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H149" s="5" t="str">
         <f>IF(E149="","",IF(AND(F149="نعم",G149="نعم"),"جرد + مراجعة",IF(F149="نعم","جرد فقط",IF(G149="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I149" s="9">
         <f>IF(H149="جرد + مراجعة",الإعدادات!$B$2,IF(H149="مراجعة فقط",الإعدادات!$B$3,IF(H149="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="n"/>
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="B150" s="5" t="str">
         <f>IF(A150="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A150,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الجمعة</v>
       </c>
       <c r="C150" s="5" t="str">
         <f>IF(A150="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A150,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D150" s="4" t="n"/>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>د. محمد فؤاد</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H150" s="5" t="str">
         <f>IF(E150="","",IF(AND(F150="نعم",G150="نعم"),"جرد + مراجعة",IF(F150="نعم","جرد فقط",IF(G150="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I150" s="9">
         <f>IF(H150="جرد + مراجعة",الإعدادات!$B$2,IF(H150="مراجعة فقط",الإعدادات!$B$3,IF(H150="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="151">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>6700</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>5950</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="9">
@@ -961,11 +961,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>24250</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>24250</v>
+        <v>24750</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1000"/>
+  <dimension ref="A1:X1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1027,7 +1027,8 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1164,6 +1165,12 @@
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
+          <t>السبت
+2026-10-17</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1257,9 +1264,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,V$1000)</f>
         <v>200</v>
       </c>
-      <c r="W2" s="6">
-        <f>SUM(B2:V2)</f>
-        <v>6700</v>
+      <c r="W2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="X2" s="6">
+        <f>SUM(B2:W2)</f>
+        <v>6850</v>
       </c>
     </row>
     <row r="3">
@@ -1351,9 +1362,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,V$1000)</f>
         <v>0</v>
       </c>
-      <c r="W3" s="6">
-        <f>SUM(B3:V3)</f>
-        <v>5950</v>
+      <c r="W3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="X3" s="6">
+        <f>SUM(B3:W3)</f>
+        <v>6100</v>
       </c>
     </row>
     <row r="4">
@@ -1445,8 +1460,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,V$1000)</f>
         <v>0</v>
       </c>
-      <c r="W4" s="6">
-        <f>SUM(B4:V4)</f>
+      <c r="W4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="6">
+        <f>SUM(B4:W4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1539,8 +1558,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,V$1000)</f>
         <v>150</v>
       </c>
-      <c r="W5" s="6">
-        <f>SUM(B5:V5)</f>
+      <c r="W5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="6">
+        <f>SUM(B5:W5)</f>
         <v>3600</v>
       </c>
     </row>
@@ -1633,9 +1656,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,V$1000)</f>
         <v>150</v>
       </c>
-      <c r="W6" s="6">
-        <f>SUM(B6:V6)</f>
-        <v>3500</v>
+      <c r="W6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>200</v>
+      </c>
+      <c r="X6" s="6">
+        <f>SUM(B6:W6)</f>
+        <v>3700</v>
       </c>
     </row>
     <row r="7">
@@ -1727,8 +1754,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,V$1000)</f>
         <v>0</v>
       </c>
-      <c r="W7" s="6">
-        <f>SUM(B7:V7)</f>
+      <c r="W7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="6">
+        <f>SUM(B7:W7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1821,8 +1852,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,V$1000)</f>
         <v>150</v>
       </c>
-      <c r="W8" s="6">
-        <f>SUM(B8:V8)</f>
+      <c r="W8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,W$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="6">
+        <f>SUM(B8:W8)</f>
         <v>150</v>
       </c>
     </row>
@@ -1918,7 +1953,11 @@
       </c>
       <c r="W9" s="8">
         <f>SUM(W2:W8)</f>
-        <v>24250</v>
+        <v>500</v>
+      </c>
+      <c r="X9" s="8">
+        <f>SUM(X2:X8)</f>
+        <v>24750</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -2025,6 +2064,11 @@
       <c r="V1000" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="W1000" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -8659,72 +8703,118 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="n"/>
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="B151" s="5" t="str">
         <f>IF(A151="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A151,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C151" s="5" t="str">
         <f>IF(A151="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A151,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D151" s="4" t="n"/>
-      <c r="E151" s="4" t="n"/>
-      <c r="F151" s="4" t="n"/>
-      <c r="G151" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H151" s="5" t="str">
         <f>IF(E151="","",IF(AND(F151="نعم",G151="نعم"),"جرد + مراجعة",IF(F151="نعم","جرد فقط",IF(G151="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I151" s="9">
         <f>IF(H151="جرد + مراجعة",الإعدادات!$B$2,IF(H151="مراجعة فقط",الإعدادات!$B$3,IF(H151="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="n"/>
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="B152" s="5" t="str">
         <f>IF(A152="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A152,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C152" s="5" t="str">
         <f>IF(A152="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A152,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D152" s="4" t="n"/>
-      <c r="E152" s="4" t="n"/>
-      <c r="F152" s="4" t="n"/>
-      <c r="G152" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr"/>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H152" s="5" t="str">
         <f>IF(E152="","",IF(AND(F152="نعم",G152="نعم"),"جرد + مراجعة",IF(F152="نعم","جرد فقط",IF(G152="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I152" s="9">
         <f>IF(H152="جرد + مراجعة",الإعدادات!$B$2,IF(H152="مراجعة فقط",الإعدادات!$B$3,IF(H152="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="n"/>
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="B153" s="5" t="str">
         <f>IF(A153="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A153,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>السبت</v>
       </c>
       <c r="C153" s="5" t="str">
         <f>IF(A153="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A153,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D153" s="4" t="n"/>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="4" t="n"/>
-      <c r="G153" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D153" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H153" s="5" t="str">
         <f>IF(E153="","",IF(AND(F153="نعم",G153="نعم"),"جرد + مراجعة",IF(F153="نعم","جرد فقط",IF(G153="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I153" s="9">
         <f>IF(H153="جرد + مراجعة",الإعدادات!$B$2,IF(H153="مراجعة فقط",الإعدادات!$B$3,IF(H153="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="154">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>6850</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>6100</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>3700</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="9">
@@ -961,11 +961,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>24750</v>
+        <v>25250</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>24750</v>
+        <v>25250</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1000"/>
+  <dimension ref="A1:Y1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1028,7 +1028,8 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1171,6 +1172,12 @@
       </c>
       <c r="X1" s="3" t="inlineStr">
         <is>
+          <t>الأحد
+2026-10-18</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1268,9 +1275,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,W$1000)</f>
         <v>150</v>
       </c>
-      <c r="X2" s="6">
-        <f>SUM(B2:W2)</f>
-        <v>6850</v>
+      <c r="X2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>200</v>
+      </c>
+      <c r="Y2" s="6">
+        <f>SUM(B2:X2)</f>
+        <v>7050</v>
       </c>
     </row>
     <row r="3">
@@ -1366,9 +1377,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,W$1000)</f>
         <v>150</v>
       </c>
-      <c r="X3" s="6">
-        <f>SUM(B3:W3)</f>
-        <v>6100</v>
+      <c r="X3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="Y3" s="6">
+        <f>SUM(B3:X3)</f>
+        <v>6250</v>
       </c>
     </row>
     <row r="4">
@@ -1464,8 +1479,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,W$1000)</f>
         <v>0</v>
       </c>
-      <c r="X4" s="6">
-        <f>SUM(B4:W4)</f>
+      <c r="X4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="6">
+        <f>SUM(B4:X4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1562,8 +1581,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,W$1000)</f>
         <v>0</v>
       </c>
-      <c r="X5" s="6">
-        <f>SUM(B5:W5)</f>
+      <c r="X5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>SUM(B5:X5)</f>
         <v>3600</v>
       </c>
     </row>
@@ -1660,9 +1683,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,W$1000)</f>
         <v>200</v>
       </c>
-      <c r="X6" s="6">
-        <f>SUM(B6:W6)</f>
-        <v>3700</v>
+      <c r="X6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="Y6" s="6">
+        <f>SUM(B6:X6)</f>
+        <v>3850</v>
       </c>
     </row>
     <row r="7">
@@ -1758,8 +1785,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,W$1000)</f>
         <v>0</v>
       </c>
-      <c r="X7" s="6">
-        <f>SUM(B7:W7)</f>
+      <c r="X7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="6">
+        <f>SUM(B7:X7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1856,8 +1887,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,W$1000)</f>
         <v>0</v>
       </c>
-      <c r="X8" s="6">
-        <f>SUM(B8:W8)</f>
+      <c r="X8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,X$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="6">
+        <f>SUM(B8:X8)</f>
         <v>150</v>
       </c>
     </row>
@@ -1957,7 +1992,11 @@
       </c>
       <c r="X9" s="8">
         <f>SUM(X2:X8)</f>
-        <v>24750</v>
+        <v>500</v>
+      </c>
+      <c r="Y9" s="8">
+        <f>SUM(Y2:Y8)</f>
+        <v>25250</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -2069,6 +2108,11 @@
       <c r="W1000" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="X1000" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8818,72 +8862,118 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="n"/>
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="B154" s="5" t="str">
         <f>IF(A154="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A154,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C154" s="5" t="str">
         <f>IF(A154="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A154,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D154" s="4" t="n"/>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="4" t="n"/>
-      <c r="G154" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H154" s="5" t="str">
         <f>IF(E154="","",IF(AND(F154="نعم",G154="نعم"),"جرد + مراجعة",IF(F154="نعم","جرد فقط",IF(G154="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I154" s="9">
         <f>IF(H154="جرد + مراجعة",الإعدادات!$B$2,IF(H154="مراجعة فقط",الإعدادات!$B$3,IF(H154="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="n"/>
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="B155" s="5" t="str">
         <f>IF(A155="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A155,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C155" s="5" t="str">
         <f>IF(A155="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A155,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D155" s="4" t="n"/>
-      <c r="E155" s="4" t="n"/>
-      <c r="F155" s="4" t="n"/>
-      <c r="G155" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D155" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H155" s="5" t="str">
         <f>IF(E155="","",IF(AND(F155="نعم",G155="نعم"),"جرد + مراجعة",IF(F155="نعم","جرد فقط",IF(G155="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I155" s="9">
         <f>IF(H155="جرد + مراجعة",الإعدادات!$B$2,IF(H155="مراجعة فقط",الإعدادات!$B$3,IF(H155="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="4" t="n"/>
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="B156" s="5" t="str">
         <f>IF(A156="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A156,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأحد</v>
       </c>
       <c r="C156" s="5" t="str">
         <f>IF(A156="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A156,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D156" s="4" t="n"/>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="4" t="n"/>
-      <c r="G156" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H156" s="5" t="str">
         <f>IF(E156="","",IF(AND(F156="نعم",G156="نعم"),"جرد + مراجعة",IF(F156="نعم","جرد فقط",IF(G156="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I156" s="9">
         <f>IF(H156="جرد + مراجعة",الإعدادات!$B$2,IF(H156="مراجعة فقط",الإعدادات!$B$3,IF(H156="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="157">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>7050</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>6250</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>3850</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="9">
@@ -961,11 +961,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>25250</v>
+        <v>26250</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>25250</v>
+        <v>26250</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1000"/>
+  <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1029,7 +1029,8 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1178,6 +1179,12 @@
       </c>
       <c r="Y1" s="3" t="inlineStr">
         <is>
+          <t>الاثنين
+2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1279,9 +1286,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,X$1000)</f>
         <v>200</v>
       </c>
-      <c r="Y2" s="6">
-        <f>SUM(B2:X2)</f>
-        <v>7050</v>
+      <c r="Y2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="Z2" s="6">
+        <f>SUM(B2:Y2)</f>
+        <v>7350</v>
       </c>
     </row>
     <row r="3">
@@ -1381,9 +1392,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,X$1000)</f>
         <v>150</v>
       </c>
-      <c r="Y3" s="6">
-        <f>SUM(B3:X3)</f>
-        <v>6250</v>
+      <c r="Y3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="Z3" s="6">
+        <f>SUM(B3:Y3)</f>
+        <v>6550</v>
       </c>
     </row>
     <row r="4">
@@ -1483,8 +1498,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,X$1000)</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="6">
-        <f>SUM(B4:X4)</f>
+      <c r="Y4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="6">
+        <f>SUM(B4:Y4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1585,8 +1604,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,X$1000)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="6">
-        <f>SUM(B5:X5)</f>
+      <c r="Y5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="6">
+        <f>SUM(B5:Y5)</f>
         <v>3600</v>
       </c>
     </row>
@@ -1687,9 +1710,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,X$1000)</f>
         <v>150</v>
       </c>
-      <c r="Y6" s="6">
-        <f>SUM(B6:X6)</f>
-        <v>3850</v>
+      <c r="Y6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="Z6" s="6">
+        <f>SUM(B6:Y6)</f>
+        <v>4250</v>
       </c>
     </row>
     <row r="7">
@@ -1789,8 +1816,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,X$1000)</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="6">
-        <f>SUM(B7:X7)</f>
+      <c r="Y7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="6">
+        <f>SUM(B7:Y7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1891,8 +1922,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,X$1000)</f>
         <v>0</v>
       </c>
-      <c r="Y8" s="6">
-        <f>SUM(B8:X8)</f>
+      <c r="Y8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,Y$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="6">
+        <f>SUM(B8:Y8)</f>
         <v>150</v>
       </c>
     </row>
@@ -1996,7 +2031,11 @@
       </c>
       <c r="Y9" s="8">
         <f>SUM(Y2:Y8)</f>
-        <v>25250</v>
+        <v>1000</v>
+      </c>
+      <c r="Z9" s="8">
+        <f>SUM(Z2:Z8)</f>
+        <v>26250</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -2113,6 +2152,11 @@
       <c r="X1000" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Y1000" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -8977,141 +9021,233 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="n"/>
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="B157" s="5" t="str">
         <f>IF(A157="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A157,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C157" s="5" t="str">
         <f>IF(A157="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A157,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D157" s="4" t="n"/>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="4" t="n"/>
-      <c r="G157" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D157" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H157" s="5" t="str">
         <f>IF(E157="","",IF(AND(F157="نعم",G157="نعم"),"جرد + مراجعة",IF(F157="نعم","جرد فقط",IF(G157="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I157" s="9">
         <f>IF(H157="جرد + مراجعة",الإعدادات!$B$2,IF(H157="مراجعة فقط",الإعدادات!$B$3,IF(H157="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="n"/>
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="B158" s="5" t="str">
         <f>IF(A158="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A158,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C158" s="5" t="str">
         <f>IF(A158="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A158,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D158" s="4" t="n"/>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="4" t="n"/>
-      <c r="G158" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D158" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr"/>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H158" s="5" t="str">
         <f>IF(E158="","",IF(AND(F158="نعم",G158="نعم"),"جرد + مراجعة",IF(F158="نعم","جرد فقط",IF(G158="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I158" s="9">
         <f>IF(H158="جرد + مراجعة",الإعدادات!$B$2,IF(H158="مراجعة فقط",الإعدادات!$B$3,IF(H158="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="4" t="n"/>
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="B159" s="5" t="str">
         <f>IF(A159="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A159,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C159" s="5" t="str">
         <f>IF(A159="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A159,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D159" s="4" t="n"/>
-      <c r="E159" s="4" t="n"/>
-      <c r="F159" s="4" t="n"/>
-      <c r="G159" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D159" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H159" s="5" t="str">
         <f>IF(E159="","",IF(AND(F159="نعم",G159="نعم"),"جرد + مراجعة",IF(F159="نعم","جرد فقط",IF(G159="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I159" s="9">
         <f>IF(H159="جرد + مراجعة",الإعدادات!$B$2,IF(H159="مراجعة فقط",الإعدادات!$B$3,IF(H159="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="n"/>
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="B160" s="5" t="str">
         <f>IF(A160="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A160,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C160" s="5" t="str">
         <f>IF(A160="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A160,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D160" s="4" t="n"/>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="4" t="n"/>
-      <c r="G160" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D160" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H160" s="5" t="str">
         <f>IF(E160="","",IF(AND(F160="نعم",G160="نعم"),"جرد + مراجعة",IF(F160="نعم","جرد فقط",IF(G160="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I160" s="9">
         <f>IF(H160="جرد + مراجعة",الإعدادات!$B$2,IF(H160="مراجعة فقط",الإعدادات!$B$3,IF(H160="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="n"/>
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="B161" s="5" t="str">
         <f>IF(A161="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A161,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C161" s="5" t="str">
         <f>IF(A161="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A161,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D161" s="4" t="n"/>
-      <c r="E161" s="4" t="n"/>
-      <c r="F161" s="4" t="n"/>
-      <c r="G161" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr"/>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H161" s="5" t="str">
         <f>IF(E161="","",IF(AND(F161="نعم",G161="نعم"),"جرد + مراجعة",IF(F161="نعم","جرد فقط",IF(G161="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I161" s="9">
         <f>IF(H161="جرد + مراجعة",الإعدادات!$B$2,IF(H161="مراجعة فقط",الإعدادات!$B$3,IF(H161="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="n"/>
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="B162" s="5" t="str">
         <f>IF(A162="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A162,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الاثنين</v>
       </c>
       <c r="C162" s="5" t="str">
         <f>IF(A162="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A162,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D162" s="4" t="n"/>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="n"/>
-      <c r="G162" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr"/>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H162" s="5" t="str">
         <f>IF(E162="","",IF(AND(F162="نعم",G162="نعم"),"جرد + مراجعة",IF(F162="نعم","جرد فقط",IF(G162="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I162" s="9">
         <f>IF(H162="جرد + مراجعة",الإعدادات!$B$2,IF(H162="مراجعة فقط",الإعدادات!$B$3,IF(H162="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>7350</v>
+        <v>7750</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>6550</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="6">
@@ -961,11 +961,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>26250</v>
+        <v>26950</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>26250</v>
+        <v>26950</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:AA1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1030,7 +1030,8 @@
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1185,6 +1186,12 @@
       </c>
       <c r="Z1" s="3" t="inlineStr">
         <is>
+          <t>الثلاثاء
+2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1290,9 +1297,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>300</v>
       </c>
-      <c r="Z2" s="6">
-        <f>SUM(B2:Y2)</f>
-        <v>7350</v>
+      <c r="Z2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="AA2" s="6">
+        <f>SUM(B2:Z2)</f>
+        <v>7750</v>
       </c>
     </row>
     <row r="3">
@@ -1396,9 +1407,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>300</v>
       </c>
-      <c r="Z3" s="6">
-        <f>SUM(B3:Y3)</f>
-        <v>6550</v>
+      <c r="Z3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="AA3" s="6">
+        <f>SUM(B3:Z3)</f>
+        <v>6850</v>
       </c>
     </row>
     <row r="4">
@@ -1502,8 +1517,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="6">
-        <f>SUM(B4:Y4)</f>
+      <c r="Z4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="6">
+        <f>SUM(B4:Z4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1608,8 +1627,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="6">
-        <f>SUM(B5:Y5)</f>
+      <c r="Z5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="6">
+        <f>SUM(B5:Z5)</f>
         <v>3600</v>
       </c>
     </row>
@@ -1714,8 +1737,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>400</v>
       </c>
-      <c r="Z6" s="6">
-        <f>SUM(B6:Y6)</f>
+      <c r="Z6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="6">
+        <f>SUM(B6:Z6)</f>
         <v>4250</v>
       </c>
     </row>
@@ -1820,8 +1847,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="6">
-        <f>SUM(B7:Y7)</f>
+      <c r="Z7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="6">
+        <f>SUM(B7:Z7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1926,8 +1957,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,Y$1000)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="6">
-        <f>SUM(B8:Y8)</f>
+      <c r="Z8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,Z$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="6">
+        <f>SUM(B8:Z8)</f>
         <v>150</v>
       </c>
     </row>
@@ -2035,7 +2070,11 @@
       </c>
       <c r="Z9" s="8">
         <f>SUM(Z2:Z8)</f>
-        <v>26250</v>
+        <v>700</v>
+      </c>
+      <c r="AA9" s="8">
+        <f>SUM(AA2:AA8)</f>
+        <v>26950</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -2157,6 +2196,11 @@
       <c r="Y1000" t="inlineStr">
         <is>
           <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z1000" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -9251,95 +9295,159 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="n"/>
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="B163" s="5" t="str">
         <f>IF(A163="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A163,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C163" s="5" t="str">
         <f>IF(A163="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A163,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D163" s="4" t="n"/>
-      <c r="E163" s="4" t="n"/>
-      <c r="F163" s="4" t="n"/>
-      <c r="G163" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H163" s="5" t="str">
         <f>IF(E163="","",IF(AND(F163="نعم",G163="نعم"),"جرد + مراجعة",IF(F163="نعم","جرد فقط",IF(G163="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I163" s="9">
         <f>IF(H163="جرد + مراجعة",الإعدادات!$B$2,IF(H163="مراجعة فقط",الإعدادات!$B$3,IF(H163="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="n"/>
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="B164" s="5" t="str">
         <f>IF(A164="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A164,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C164" s="5" t="str">
         <f>IF(A164="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A164,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D164" s="4" t="n"/>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="4" t="n"/>
-      <c r="G164" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D164" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr"/>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H164" s="5" t="str">
         <f>IF(E164="","",IF(AND(F164="نعم",G164="نعم"),"جرد + مراجعة",IF(F164="نعم","جرد فقط",IF(G164="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I164" s="9">
         <f>IF(H164="جرد + مراجعة",الإعدادات!$B$2,IF(H164="مراجعة فقط",الإعدادات!$B$3,IF(H164="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="n"/>
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="B165" s="5" t="str">
         <f>IF(A165="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A165,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C165" s="5" t="str">
         <f>IF(A165="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A165,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D165" s="4" t="n"/>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="4" t="n"/>
-      <c r="G165" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H165" s="5" t="str">
         <f>IF(E165="","",IF(AND(F165="نعم",G165="نعم"),"جرد + مراجعة",IF(F165="نعم","جرد فقط",IF(G165="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I165" s="9">
         <f>IF(H165="جرد + مراجعة",الإعدادات!$B$2,IF(H165="مراجعة فقط",الإعدادات!$B$3,IF(H165="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="n"/>
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="B166" s="5" t="str">
         <f>IF(A166="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A166,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الثلاثاء</v>
       </c>
       <c r="C166" s="5" t="str">
         <f>IF(A166="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A166,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D166" s="4" t="n"/>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="4" t="n"/>
-      <c r="G166" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H166" s="5" t="str">
         <f>IF(E166="","",IF(AND(F166="نعم",G166="نعم"),"جرد + مراجعة",IF(F166="نعم","جرد فقط",IF(G166="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I166" s="9">
         <f>IF(H166="جرد + مراجعة",الإعدادات!$B$2,IF(H166="مراجعة فقط",الإعدادات!$B$3,IF(H166="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="167">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -600,11 +600,11 @@
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>7750</v>
+        <v>8050</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>6850</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>4250</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="9">
@@ -961,11 +961,11 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>26950</v>
+        <v>27950</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>26950</v>
+        <v>27950</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:AB1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1031,7 +1031,8 @@
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1192,6 +1193,12 @@
       </c>
       <c r="AA1" s="3" t="inlineStr">
         <is>
+          <t>الأربعاء
+2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1301,9 +1308,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>400</v>
       </c>
-      <c r="AA2" s="6">
-        <f>SUM(B2:Z2)</f>
-        <v>7750</v>
+      <c r="AA2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="AB2" s="6">
+        <f>SUM(B2:AA2)</f>
+        <v>8050</v>
       </c>
     </row>
     <row r="3">
@@ -1411,9 +1422,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>300</v>
       </c>
-      <c r="AA3" s="6">
-        <f>SUM(B3:Z3)</f>
-        <v>6850</v>
+      <c r="AA3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="AB3" s="6">
+        <f>SUM(B3:AA3)</f>
+        <v>7150</v>
       </c>
     </row>
     <row r="4">
@@ -1521,8 +1536,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>0</v>
       </c>
-      <c r="AA4" s="6">
-        <f>SUM(B4:Z4)</f>
+      <c r="AA4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="6">
+        <f>SUM(B4:AA4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1631,8 +1650,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="6">
-        <f>SUM(B5:Z5)</f>
+      <c r="AA5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="6">
+        <f>SUM(B5:AA5)</f>
         <v>3600</v>
       </c>
     </row>
@@ -1741,9 +1764,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="6">
-        <f>SUM(B6:Z6)</f>
-        <v>4250</v>
+      <c r="AA6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>400</v>
+      </c>
+      <c r="AB6" s="6">
+        <f>SUM(B6:AA6)</f>
+        <v>4650</v>
       </c>
     </row>
     <row r="7">
@@ -1851,8 +1878,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="6">
-        <f>SUM(B7:Z7)</f>
+      <c r="AA7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="6">
+        <f>SUM(B7:AA7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1961,8 +1992,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,Z$1000)</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="6">
-        <f>SUM(B8:Z8)</f>
+      <c r="AA8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,AA$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="6">
+        <f>SUM(B8:AA8)</f>
         <v>150</v>
       </c>
     </row>
@@ -2074,7 +2109,11 @@
       </c>
       <c r="AA9" s="8">
         <f>SUM(AA2:AA8)</f>
-        <v>26950</v>
+        <v>1000</v>
+      </c>
+      <c r="AB9" s="8">
+        <f>SUM(AB2:AB8)</f>
+        <v>27950</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -2201,6 +2240,11 @@
       <c r="Z1000" t="inlineStr">
         <is>
           <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA1000" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9451,141 +9495,233 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="n"/>
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="B167" s="5" t="str">
         <f>IF(A167="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A167,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C167" s="5" t="str">
         <f>IF(A167="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A167,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D167" s="4" t="n"/>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="4" t="n"/>
-      <c r="G167" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H167" s="5" t="str">
         <f>IF(E167="","",IF(AND(F167="نعم",G167="نعم"),"جرد + مراجعة",IF(F167="نعم","جرد فقط",IF(G167="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I167" s="9">
         <f>IF(H167="جرد + مراجعة",الإعدادات!$B$2,IF(H167="مراجعة فقط",الإعدادات!$B$3,IF(H167="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="4" t="n"/>
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="B168" s="5" t="str">
         <f>IF(A168="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A168,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C168" s="5" t="str">
         <f>IF(A168="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A168,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D168" s="4" t="n"/>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="4" t="n"/>
-      <c r="G168" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr"/>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H168" s="5" t="str">
         <f>IF(E168="","",IF(AND(F168="نعم",G168="نعم"),"جرد + مراجعة",IF(F168="نعم","جرد فقط",IF(G168="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I168" s="9">
         <f>IF(H168="جرد + مراجعة",الإعدادات!$B$2,IF(H168="مراجعة فقط",الإعدادات!$B$3,IF(H168="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="n"/>
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="B169" s="5" t="str">
         <f>IF(A169="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A169,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C169" s="5" t="str">
         <f>IF(A169="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A169,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D169" s="4" t="n"/>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D169" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr"/>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H169" s="5" t="str">
         <f>IF(E169="","",IF(AND(F169="نعم",G169="نعم"),"جرد + مراجعة",IF(F169="نعم","جرد فقط",IF(G169="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I169" s="9">
         <f>IF(H169="جرد + مراجعة",الإعدادات!$B$2,IF(H169="مراجعة فقط",الإعدادات!$B$3,IF(H169="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="n"/>
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="B170" s="5" t="str">
         <f>IF(A170="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A170,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C170" s="5" t="str">
         <f>IF(A170="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A170,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D170" s="4" t="n"/>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="4" t="n"/>
-      <c r="G170" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H170" s="5" t="str">
         <f>IF(E170="","",IF(AND(F170="نعم",G170="نعم"),"جرد + مراجعة",IF(F170="نعم","جرد فقط",IF(G170="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I170" s="9">
         <f>IF(H170="جرد + مراجعة",الإعدادات!$B$2,IF(H170="مراجعة فقط",الإعدادات!$B$3,IF(H170="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="n"/>
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="B171" s="5" t="str">
         <f>IF(A171="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A171,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C171" s="5" t="str">
         <f>IF(A171="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A171,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D171" s="4" t="n"/>
-      <c r="E171" s="4" t="n"/>
-      <c r="F171" s="4" t="n"/>
-      <c r="G171" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D171" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr"/>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H171" s="5" t="str">
         <f>IF(E171="","",IF(AND(F171="نعم",G171="نعم"),"جرد + مراجعة",IF(F171="نعم","جرد فقط",IF(G171="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I171" s="9">
         <f>IF(H171="جرد + مراجعة",الإعدادات!$B$2,IF(H171="مراجعة فقط",الإعدادات!$B$3,IF(H171="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="n"/>
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="B172" s="5" t="str">
         <f>IF(A172="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A172,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الأربعاء</v>
       </c>
       <c r="C172" s="5" t="str">
         <f>IF(A172="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A172,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D172" s="4" t="n"/>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="n"/>
-      <c r="G172" s="4" t="n"/>
+        <v>الرياض</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr"/>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H172" s="5" t="str">
         <f>IF(E172="","",IF(AND(F172="نعم",G172="نعم"),"جرد + مراجعة",IF(F172="نعم","جرد فقط",IF(G172="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I172" s="9">
         <f>IF(H172="جرد + مراجعة",الإعدادات!$B$2,IF(H172="مراجعة فقط",الإعدادات!$B$3,IF(H172="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="173">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -596,15 +596,15 @@
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>8050</v>
+        <v>8350</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5">
         <f>IF(A5="","",COUNTIFS(السجل!$E$2:$E$1000,A5,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -627,11 +627,11 @@
       </c>
       <c r="E5" s="5">
         <f>IF(A5="","",SUM(B5:D5))</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="6">
         <f>IF(A5="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A5))</f>
-        <v>7150</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>4650</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="9">
@@ -961,23 +961,23 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>27950</v>
+        <v>28550</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>27950</v>
+        <v>28550</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AC1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,8 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1199,6 +1200,12 @@
       </c>
       <c r="AB1" s="3" t="inlineStr">
         <is>
+          <t>الخميس
+2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
           <t>الإجمالي</t>
         </is>
       </c>
@@ -1312,9 +1319,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>300</v>
       </c>
-      <c r="AB2" s="6">
-        <f>SUM(B2:AA2)</f>
-        <v>8050</v>
+      <c r="AB2" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>300</v>
+      </c>
+      <c r="AC2" s="6">
+        <f>SUM(B2:AB2)</f>
+        <v>8350</v>
       </c>
     </row>
     <row r="3">
@@ -1426,9 +1437,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>300</v>
       </c>
-      <c r="AB3" s="6">
-        <f>SUM(B3:AA3)</f>
-        <v>7150</v>
+      <c r="AB3" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A3,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="AC3" s="6">
+        <f>SUM(B3:AB3)</f>
+        <v>7300</v>
       </c>
     </row>
     <row r="4">
@@ -1540,8 +1555,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>0</v>
       </c>
-      <c r="AB4" s="6">
-        <f>SUM(B4:AA4)</f>
+      <c r="AB4" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="6">
+        <f>SUM(B4:AB4)</f>
         <v>1650</v>
       </c>
     </row>
@@ -1654,8 +1673,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>0</v>
       </c>
-      <c r="AB5" s="6">
-        <f>SUM(B5:AA5)</f>
+      <c r="AB5" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A5,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AC5" s="6">
+        <f>SUM(B5:AB5)</f>
         <v>3600</v>
       </c>
     </row>
@@ -1768,9 +1791,13 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>400</v>
       </c>
-      <c r="AB6" s="6">
-        <f>SUM(B6:AA6)</f>
-        <v>4650</v>
+      <c r="AB6" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>150</v>
+      </c>
+      <c r="AC6" s="6">
+        <f>SUM(B6:AB6)</f>
+        <v>4800</v>
       </c>
     </row>
     <row r="7">
@@ -1882,8 +1909,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="6">
-        <f>SUM(B7:AA7)</f>
+      <c r="AB7" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="6">
+        <f>SUM(B7:AB7)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1996,8 +2027,12 @@
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,AA$1000)</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="6">
-        <f>SUM(B8:AA8)</f>
+      <c r="AB8" s="9">
+        <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A8,السجل!$A$2:$A$1000,AB$1000)</f>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="6">
+        <f>SUM(B8:AB8)</f>
         <v>150</v>
       </c>
     </row>
@@ -2113,7 +2148,11 @@
       </c>
       <c r="AB9" s="8">
         <f>SUM(AB2:AB8)</f>
-        <v>27950</v>
+        <v>600</v>
+      </c>
+      <c r="AC9" s="8">
+        <f>SUM(AC2:AC8)</f>
+        <v>28550</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -2245,6 +2284,11 @@
       <c r="AA1000" t="inlineStr">
         <is>
           <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB1000" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -9725,95 +9769,155 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="n"/>
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="B173" s="5" t="str">
         <f>IF(A173="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A173,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C173" s="5" t="str">
         <f>IF(A173="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A173,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D173" s="4" t="n"/>
-      <c r="E173" s="4" t="n"/>
-      <c r="F173" s="4" t="n"/>
-      <c r="G173" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D173" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr"/>
       <c r="H173" s="5" t="str">
         <f>IF(E173="","",IF(AND(F173="نعم",G173="نعم"),"جرد + مراجعة",IF(F173="نعم","جرد فقط",IF(G173="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد فقط</v>
       </c>
       <c r="I173" s="9">
         <f>IF(H173="جرد + مراجعة",الإعدادات!$B$2,IF(H173="مراجعة فقط",الإعدادات!$B$3,IF(H173="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="n"/>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="B174" s="5" t="str">
         <f>IF(A174="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A174,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C174" s="5" t="str">
         <f>IF(A174="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A174,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D174" s="4" t="n"/>
-      <c r="E174" s="4" t="n"/>
-      <c r="F174" s="4" t="n"/>
-      <c r="G174" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H174" s="5" t="str">
         <f>IF(E174="","",IF(AND(F174="نعم",G174="نعم"),"جرد + مراجعة",IF(F174="نعم","جرد فقط",IF(G174="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I174" s="9">
         <f>IF(H174="جرد + مراجعة",الإعدادات!$B$2,IF(H174="مراجعة فقط",الإعدادات!$B$3,IF(H174="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="n"/>
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="B175" s="5" t="str">
         <f>IF(A175="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A175,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C175" s="5" t="str">
         <f>IF(A175="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A175,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D175" s="4" t="n"/>
-      <c r="E175" s="4" t="n"/>
-      <c r="F175" s="4" t="n"/>
-      <c r="G175" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D175" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr"/>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H175" s="5" t="str">
         <f>IF(E175="","",IF(AND(F175="نعم",G175="نعم"),"جرد + مراجعة",IF(F175="نعم","جرد فقط",IF(G175="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I175" s="9">
         <f>IF(H175="جرد + مراجعة",الإعدادات!$B$2,IF(H175="مراجعة فقط",الإعدادات!$B$3,IF(H175="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="n"/>
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="B176" s="5" t="str">
         <f>IF(A176="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A176,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C176" s="5" t="str">
         <f>IF(A176="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A176,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D176" s="4" t="n"/>
-      <c r="E176" s="4" t="n"/>
-      <c r="F176" s="4" t="n"/>
-      <c r="G176" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr"/>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H176" s="5" t="str">
         <f>IF(E176="","",IF(AND(F176="نعم",G176="نعم"),"جرد + مراجعة",IF(F176="نعم","جرد فقط",IF(G176="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I176" s="9">
         <f>IF(H176="جرد + مراجعة",الإعدادات!$B$2,IF(H176="مراجعة فقط",الإعدادات!$B$3,IF(H176="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="177">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد + مراجعة"))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
@@ -596,7 +596,7 @@
       </c>
       <c r="D4" s="5">
         <f>IF(A4="","",COUNTIFS(السجل!$E$2:$E$1000,A4,السجل!$H$2:$H$1000,"جرد فقط"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5">
         <f>IF(A4="","",SUM(B4:D4))</f>
@@ -604,7 +604,7 @@
       </c>
       <c r="F4" s="6">
         <f>IF(A4="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A4))</f>
-        <v>8350</v>
+        <v>8450</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5">
         <f>IF(A8="","",COUNTIFS(السجل!$E$2:$E$1000,A8,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -708,11 +708,11 @@
       </c>
       <c r="E8" s="5">
         <f>IF(A8="","",SUM(B8:D8))</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="6">
         <f>IF(A8="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A8))</f>
-        <v>4800</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="9">
@@ -961,23 +961,23 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B4:B18)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>28550</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>28550</v>
+        <v>28800</v>
       </c>
     </row>
   </sheetData>
@@ -1321,11 +1321,11 @@
       </c>
       <c r="AB2" s="9">
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A2,السجل!$A$2:$A$1000,AB$1000)</f>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC2" s="6">
         <f>SUM(B2:AB2)</f>
-        <v>8350</v>
+        <v>8450</v>
       </c>
     </row>
     <row r="3">
@@ -1793,11 +1793,11 @@
       </c>
       <c r="AB6" s="9">
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A6,السجل!$A$2:$A$1000,AB$1000)</f>
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="AC6" s="6">
         <f>SUM(B6:AB6)</f>
-        <v>4800</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="7">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="AB9" s="8">
         <f>SUM(AB2:AB8)</f>
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="AC9" s="8">
         <f>SUM(AC2:AC8)</f>
-        <v>28550</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -9795,14 +9795,18 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="G173" s="4" t="inlineStr"/>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H173" s="5" t="str">
         <f>IF(E173="","",IF(AND(F173="نعم",G173="نعم"),"جرد + مراجعة",IF(F173="نعم","جرد فقط",IF(G173="نعم","مراجعة فقط",""))))</f>
-        <v>جرد فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I173" s="9">
         <f>IF(H173="جرد + مراجعة",الإعدادات!$B$2,IF(H173="مراجعة فقط",الإعدادات!$B$3,IF(H173="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="174">
@@ -9820,18 +9824,14 @@
         <v>الخرج</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9839,11 +9839,11 @@
       </c>
       <c r="H174" s="5" t="str">
         <f>IF(E174="","",IF(AND(F174="نعم",G174="نعم"),"جرد + مراجعة",IF(F174="نعم","جرد فقط",IF(G174="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I174" s="9">
         <f>IF(H174="جرد + مراجعة",الإعدادات!$B$2,IF(H174="مراجعة فقط",الإعدادات!$B$3,IF(H174="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="175">
@@ -9865,10 +9865,14 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9876,11 +9880,11 @@
       </c>
       <c r="H175" s="5" t="str">
         <f>IF(E175="","",IF(AND(F175="نعم",G175="نعم"),"جرد + مراجعة",IF(F175="نعم","جرد فقط",IF(G175="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I175" s="9">
         <f>IF(H175="جرد + مراجعة",الإعدادات!$B$2,IF(H175="مراجعة فقط",الإعدادات!$B$3,IF(H175="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="176">
@@ -9902,7 +9906,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr"/>
@@ -9921,26 +9925,40 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="n"/>
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="B177" s="5" t="str">
         <f>IF(A177="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$29,MATCH(A177,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
+        <v>الخميس</v>
       </c>
       <c r="C177" s="5" t="str">
         <f>IF(A177="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$29,MATCH(A177,'جدول الجرد'!$B$2:$B$29,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D177" s="4" t="n"/>
-      <c r="E177" s="4" t="n"/>
-      <c r="F177" s="4" t="n"/>
-      <c r="G177" s="4" t="n"/>
+        <v>الخرج</v>
+      </c>
+      <c r="D177" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr"/>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="H177" s="5" t="str">
         <f>IF(E177="","",IF(AND(F177="نعم",G177="نعم"),"جرد + مراجعة",IF(F177="نعم","جرد فقط",IF(G177="نعم","مراجعة فقط",""))))</f>
-        <v/>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I177" s="9">
         <f>IF(H177="جرد + مراجعة",الإعدادات!$B$2,IF(H177="مراجعة فقط",الإعدادات!$B$3,IF(H177="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">

--- a/inventory/jard_payroll.xlsx
+++ b/inventory/jard_payroll.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="C6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5">
         <f>IF(A6="","",COUNTIFS(السجل!$E$2:$E$1000,A6,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -654,11 +654,11 @@
       </c>
       <c r="E6" s="5">
         <f>IF(A6="","",SUM(B6:D6))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6">
         <f>IF(A6="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A6))</f>
-        <v>1650</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="7">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"مراجعة فقط"))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="5">
         <f>IF(A9="","",COUNTIFS(السجل!$E$2:$E$1000,A9,السجل!$H$2:$H$1000,"جرد فقط"))</f>
@@ -735,11 +735,11 @@
       </c>
       <c r="E9" s="5">
         <f>IF(A9="","",SUM(B9:D9))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" s="6">
         <f>IF(A9="","",SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,A9))</f>
-        <v>2700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="10">
@@ -965,7 +965,7 @@
       </c>
       <c r="C19" s="7">
         <f>SUM(C4:C18)</f>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(D4:D18)</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F19" s="8">
         <f>SUM(F4:F18)</f>
-        <v>28800</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="21">
@@ -988,7 +988,7 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(السجل!$I$2:$I$1000)</f>
-        <v>28800</v>
+        <v>28650</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="W4" s="9">
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,W$1000)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="X4" s="9">
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A4,السجل!$A$2:$A$1000,X$1000)</f>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AD4" s="6">
         <f>SUM(B4:AC4)</f>
-        <v>1650</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="5">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T7" s="9">
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,T$1000)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="U7" s="9">
         <f>SUMIFS(السجل!$I$2:$I$1000,السجل!$E$2:$E$1000,$A7,السجل!$A$2:$A$1000,U$1000)</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AD7" s="6">
         <f>SUM(B7:AC7)</f>
-        <v>2700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="T9" s="8">
         <f>SUM(T2:T8)</f>
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="U9" s="8">
         <f>SUM(U2:U8)</f>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="W9" s="8">
         <f>SUM(W2:W8)</f>
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="X9" s="8">
         <f>SUM(X2:X8)</f>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AD9" s="8">
         <f>SUM(AD2:AD8)</f>
-        <v>28800</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="1000" hidden="1">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>د. محمد جمال</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr"/>
@@ -8234,14 +8234,18 @@
         <v>الخرج</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8249,11 +8253,11 @@
       </c>
       <c r="H130" s="5" t="str">
         <f>IF(E130="","",IF(AND(F130="نعم",G130="نعم"),"جرد + مراجعة",IF(F130="نعم","جرد فقط",IF(G130="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I130" s="9">
         <f>IF(H130="جرد + مراجعة",الإعدادات!$B$2,IF(H130="مراجعة فقط",الإعدادات!$B$3,IF(H130="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131">
@@ -8275,14 +8279,10 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8290,11 +8290,11 @@
       </c>
       <c r="H131" s="5" t="str">
         <f>IF(E131="","",IF(AND(F131="نعم",G131="نعم"),"جرد + مراجعة",IF(F131="نعم","جرد فقط",IF(G131="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I131" s="9">
         <f>IF(H131="جرد + مراجعة",الإعدادات!$B$2,IF(H131="مراجعة فقط",الإعدادات!$B$3,IF(H131="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="132">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
@@ -8337,26 +8337,30 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B133" s="5" t="str">
         <f>IF(A133="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A133,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الثلاثاء</v>
+        <v>الأربعاء</v>
       </c>
       <c r="C133" s="5" t="str">
         <f>IF(A133="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A133,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>د. محمد جمال</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8364,33 +8368,33 @@
       </c>
       <c r="H133" s="5" t="str">
         <f>IF(E133="","",IF(AND(F133="نعم",G133="نعم"),"جرد + مراجعة",IF(F133="نعم","جرد فقط",IF(G133="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I133" s="9">
         <f>IF(H133="جرد + مراجعة",الإعدادات!$B$2,IF(H133="مراجعة فقط",الإعدادات!$B$3,IF(H133="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B134" s="5" t="str">
         <f>IF(A134="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A134,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الثلاثاء</v>
+        <v>الأربعاء</v>
       </c>
       <c r="C134" s="5" t="str">
         <f>IF(A134="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A134,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -8427,14 +8431,10 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8442,11 +8442,11 @@
       </c>
       <c r="H135" s="5" t="str">
         <f>IF(E135="","",IF(AND(F135="نعم",G135="نعم"),"جرد + مراجعة",IF(F135="نعم","جرد فقط",IF(G135="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I135" s="9">
         <f>IF(H135="جرد + مراجعة",الإعدادات!$B$2,IF(H135="مراجعة فقط",الإعدادات!$B$3,IF(H135="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="136">
@@ -8464,14 +8464,18 @@
         <v>الخرج</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8479,11 +8483,11 @@
       </c>
       <c r="H136" s="5" t="str">
         <f>IF(E136="","",IF(AND(F136="نعم",G136="نعم"),"جرد + مراجعة",IF(F136="نعم","جرد فقط",IF(G136="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I136" s="9">
         <f>IF(H136="جرد + مراجعة",الإعدادات!$B$2,IF(H136="مراجعة فقط",الإعدادات!$B$3,IF(H136="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="137">
@@ -8501,11 +8505,11 @@
         <v>الخرج</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
@@ -8542,14 +8546,10 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8557,36 +8557,40 @@
       </c>
       <c r="H138" s="5" t="str">
         <f>IF(E138="","",IF(AND(F138="نعم",G138="نعم"),"جرد + مراجعة",IF(F138="نعم","جرد فقط",IF(G138="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I138" s="9">
         <f>IF(H138="جرد + مراجعة",الإعدادات!$B$2,IF(H138="مراجعة فقط",الإعدادات!$B$3,IF(H138="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B139" s="5" t="str">
         <f>IF(A139="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A139,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الأربعاء</v>
+        <v>الخميس</v>
       </c>
       <c r="C139" s="5" t="str">
         <f>IF(A139="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A139,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
           <t>د. علي خليفة</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8594,33 +8598,33 @@
       </c>
       <c r="H139" s="5" t="str">
         <f>IF(E139="","",IF(AND(F139="نعم",G139="نعم"),"جرد + مراجعة",IF(F139="نعم","جرد فقط",IF(G139="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I139" s="9">
         <f>IF(H139="جرد + مراجعة",الإعدادات!$B$2,IF(H139="مراجعة فقط",الإعدادات!$B$3,IF(H139="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B140" s="5" t="str">
         <f>IF(A140="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A140,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الأربعاء</v>
+        <v>الخميس</v>
       </c>
       <c r="C140" s="5" t="str">
         <f>IF(A140="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A140,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr"/>
@@ -8657,14 +8661,10 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8672,11 +8672,11 @@
       </c>
       <c r="H141" s="5" t="str">
         <f>IF(E141="","",IF(AND(F141="نعم",G141="نعم"),"جرد + مراجعة",IF(F141="نعم","جرد فقط",IF(G141="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I141" s="9">
         <f>IF(H141="جرد + مراجعة",الإعدادات!$B$2,IF(H141="مراجعة فقط",الإعدادات!$B$3,IF(H141="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="142">
@@ -8694,14 +8694,18 @@
         <v>الخرج</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8709,11 +8713,11 @@
       </c>
       <c r="H142" s="5" t="str">
         <f>IF(E142="","",IF(AND(F142="نعم",G142="نعم"),"جرد + مراجعة",IF(F142="نعم","جرد فقط",IF(G142="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I142" s="9">
         <f>IF(H142="جرد + مراجعة",الإعدادات!$B$2,IF(H142="مراجعة فقط",الإعدادات!$B$3,IF(H142="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143">
@@ -8731,11 +8735,11 @@
         <v>الخرج</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr"/>
@@ -8772,14 +8776,10 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8787,36 +8787,40 @@
       </c>
       <c r="H144" s="5" t="str">
         <f>IF(E144="","",IF(AND(F144="نعم",G144="نعم"),"جرد + مراجعة",IF(F144="نعم","جرد فقط",IF(G144="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I144" s="9">
         <f>IF(H144="جرد + مراجعة",الإعدادات!$B$2,IF(H144="مراجعة فقط",الإعدادات!$B$3,IF(H144="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B145" s="5" t="str">
         <f>IF(A145="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A145,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الخميس</v>
+        <v>الجمعة</v>
       </c>
       <c r="C145" s="5" t="str">
         <f>IF(A145="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A145,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
           <t>د. حسام شلش</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8824,33 +8828,33 @@
       </c>
       <c r="H145" s="5" t="str">
         <f>IF(E145="","",IF(AND(F145="نعم",G145="نعم"),"جرد + مراجعة",IF(F145="نعم","جرد فقط",IF(G145="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I145" s="9">
         <f>IF(H145="جرد + مراجعة",الإعدادات!$B$2,IF(H145="مراجعة فقط",الإعدادات!$B$3,IF(H145="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B146" s="5" t="str">
         <f>IF(A146="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A146,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الخميس</v>
+        <v>الجمعة</v>
       </c>
       <c r="C146" s="5" t="str">
         <f>IF(A146="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A146,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr"/>
@@ -8887,14 +8891,10 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -8902,11 +8902,11 @@
       </c>
       <c r="H147" s="5" t="str">
         <f>IF(E147="","",IF(AND(F147="نعم",G147="نعم"),"جرد + مراجعة",IF(F147="نعم","جرد فقط",IF(G147="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I147" s="9">
         <f>IF(H147="جرد + مراجعة",الإعدادات!$B$2,IF(H147="مراجعة فقط",الإعدادات!$B$3,IF(H147="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="148">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
+          <t>د. محمد فؤاد</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>د. الحسن الغنيمي</t>
+          <t>د. أيمن حسين</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr"/>
@@ -8986,26 +8986,30 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B150" s="5" t="str">
         <f>IF(A150="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A150,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الجمعة</v>
+        <v>السبت</v>
       </c>
       <c r="C150" s="5" t="str">
         <f>IF(A150="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A150,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>د. محمد فؤاد</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9013,11 +9017,11 @@
       </c>
       <c r="H150" s="5" t="str">
         <f>IF(E150="","",IF(AND(F150="نعم",G150="نعم"),"جرد + مراجعة",IF(F150="نعم","جرد فقط",IF(G150="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I150" s="9">
         <f>IF(H150="جرد + مراجعة",الإعدادات!$B$2,IF(H150="مراجعة فقط",الإعدادات!$B$3,IF(H150="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151">
@@ -9039,14 +9043,10 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9054,11 +9054,11 @@
       </c>
       <c r="H151" s="5" t="str">
         <f>IF(E151="","",IF(AND(F151="نعم",G151="نعم"),"جرد + مراجعة",IF(F151="نعم","جرد فقط",IF(G151="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I151" s="9">
         <f>IF(H151="جرد + مراجعة",الإعدادات!$B$2,IF(H151="مراجعة فقط",الإعدادات!$B$3,IF(H151="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="152">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr"/>
@@ -9101,26 +9101,30 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B153" s="5" t="str">
         <f>IF(A153="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A153,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>السبت</v>
+        <v>الأحد</v>
       </c>
       <c r="C153" s="5" t="str">
         <f>IF(A153="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A153,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الخرج</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
           <t>د. حسام شلش</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9128,11 +9132,11 @@
       </c>
       <c r="H153" s="5" t="str">
         <f>IF(E153="","",IF(AND(F153="نعم",G153="نعم"),"جرد + مراجعة",IF(F153="نعم","جرد فقط",IF(G153="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I153" s="9">
         <f>IF(H153="جرد + مراجعة",الإعدادات!$B$2,IF(H153="مراجعة فقط",الإعدادات!$B$3,IF(H153="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="154">
@@ -9154,14 +9158,10 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9169,11 +9169,11 @@
       </c>
       <c r="H154" s="5" t="str">
         <f>IF(E154="","",IF(AND(F154="نعم",G154="نعم"),"جرد + مراجعة",IF(F154="نعم","جرد فقط",IF(G154="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I154" s="9">
         <f>IF(H154="جرد + مراجعة",الإعدادات!$B$2,IF(H154="مراجعة فقط",الإعدادات!$B$3,IF(H154="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="155">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr"/>
@@ -9216,26 +9216,30 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B156" s="5" t="str">
         <f>IF(A156="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A156,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الأحد</v>
+        <v>الاثنين</v>
       </c>
       <c r="C156" s="5" t="str">
         <f>IF(A156="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A156,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الخرج</v>
+        <v>الرياض</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9243,11 +9247,11 @@
       </c>
       <c r="H156" s="5" t="str">
         <f>IF(E156="","",IF(AND(F156="نعم",G156="نعم"),"جرد + مراجعة",IF(F156="نعم","جرد فقط",IF(G156="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I156" s="9">
         <f>IF(H156="جرد + مراجعة",الإعدادات!$B$2,IF(H156="مراجعة فقط",الإعدادات!$B$3,IF(H156="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157">
@@ -9269,14 +9273,10 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="H157" s="5" t="str">
         <f>IF(E157="","",IF(AND(F157="نعم",G157="نعم"),"جرد + مراجعة",IF(F157="نعم","جرد فقط",IF(G157="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I157" s="9">
         <f>IF(H157="جرد + مراجعة",الإعدادات!$B$2,IF(H157="مراجعة فقط",الإعدادات!$B$3,IF(H157="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="158">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -9343,14 +9343,18 @@
         <v>الرياض</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9358,11 +9362,11 @@
       </c>
       <c r="H159" s="5" t="str">
         <f>IF(E159="","",IF(AND(F159="نعم",G159="نعم"),"جرد + مراجعة",IF(F159="نعم","جرد فقط",IF(G159="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I159" s="9">
         <f>IF(H159="جرد + مراجعة",الإعدادات!$B$2,IF(H159="مراجعة فقط",الإعدادات!$B$3,IF(H159="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="160">
@@ -9384,14 +9388,10 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr"/>
       <c r="G160" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9399,11 +9399,11 @@
       </c>
       <c r="H160" s="5" t="str">
         <f>IF(E160="","",IF(AND(F160="نعم",G160="نعم"),"جرد + مراجعة",IF(F160="نعم","جرد فقط",IF(G160="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I160" s="9">
         <f>IF(H160="جرد + مراجعة",الإعدادات!$B$2,IF(H160="مراجعة فقط",الإعدادات!$B$3,IF(H160="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="161">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -9446,26 +9446,30 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B162" s="5" t="str">
         <f>IF(A162="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A162,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الاثنين</v>
+        <v>الثلاثاء</v>
       </c>
       <c r="C162" s="5" t="str">
         <f>IF(A162="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A162,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الرياض</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9473,11 +9477,11 @@
       </c>
       <c r="H162" s="5" t="str">
         <f>IF(E162="","",IF(AND(F162="نعم",G162="نعم"),"جرد + مراجعة",IF(F162="نعم","جرد فقط",IF(G162="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I162" s="9">
         <f>IF(H162="جرد + مراجعة",الإعدادات!$B$2,IF(H162="مراجعة فقط",الإعدادات!$B$3,IF(H162="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="163">
@@ -9499,14 +9503,10 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9514,11 +9514,11 @@
       </c>
       <c r="H163" s="5" t="str">
         <f>IF(E163="","",IF(AND(F163="نعم",G163="نعم"),"جرد + مراجعة",IF(F163="نعم","جرد فقط",IF(G163="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I163" s="9">
         <f>IF(H163="جرد + مراجعة",الإعدادات!$B$2,IF(H163="مراجعة فقط",الإعدادات!$B$3,IF(H163="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="164">
@@ -9536,14 +9536,18 @@
         <v>الرياض</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9551,11 +9555,11 @@
       </c>
       <c r="H164" s="5" t="str">
         <f>IF(E164="","",IF(AND(F164="نعم",G164="نعم"),"جرد + مراجعة",IF(F164="نعم","جرد فقط",IF(G164="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I164" s="9">
         <f>IF(H164="جرد + مراجعة",الإعدادات!$B$2,IF(H164="مراجعة فقط",الإعدادات!$B$3,IF(H164="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="165">
@@ -9577,14 +9581,10 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9592,36 +9592,40 @@
       </c>
       <c r="H165" s="5" t="str">
         <f>IF(E165="","",IF(AND(F165="نعم",G165="نعم"),"جرد + مراجعة",IF(F165="نعم","جرد فقط",IF(G165="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I165" s="9">
         <f>IF(H165="جرد + مراجعة",الإعدادات!$B$2,IF(H165="مراجعة فقط",الإعدادات!$B$3,IF(H165="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B166" s="5" t="str">
         <f>IF(A166="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A166,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الثلاثاء</v>
+        <v>الأربعاء</v>
       </c>
       <c r="C166" s="5" t="str">
         <f>IF(A166="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A166,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
         <v>الرياض</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9629,11 +9633,11 @@
       </c>
       <c r="H166" s="5" t="str">
         <f>IF(E166="","",IF(AND(F166="نعم",G166="نعم"),"جرد + مراجعة",IF(F166="نعم","جرد فقط",IF(G166="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I166" s="9">
         <f>IF(H166="جرد + مراجعة",الإعدادات!$B$2,IF(H166="مراجعة فقط",الإعدادات!$B$3,IF(H166="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167">
@@ -9655,14 +9659,10 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9670,11 +9670,11 @@
       </c>
       <c r="H167" s="5" t="str">
         <f>IF(E167="","",IF(AND(F167="نعم",G167="نعم"),"جرد + مراجعة",IF(F167="نعم","جرد فقط",IF(G167="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I167" s="9">
         <f>IF(H167="جرد + مراجعة",الإعدادات!$B$2,IF(H167="مراجعة فقط",الإعدادات!$B$3,IF(H167="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="168">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr"/>
@@ -9729,14 +9729,18 @@
         <v>الرياض</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9744,11 +9748,11 @@
       </c>
       <c r="H169" s="5" t="str">
         <f>IF(E169="","",IF(AND(F169="نعم",G169="نعم"),"جرد + مراجعة",IF(F169="نعم","جرد فقط",IF(G169="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I169" s="9">
         <f>IF(H169="جرد + مراجعة",الإعدادات!$B$2,IF(H169="مراجعة فقط",الإعدادات!$B$3,IF(H169="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170">
@@ -9770,14 +9774,10 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr"/>
       <c r="G170" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9785,11 +9785,11 @@
       </c>
       <c r="H170" s="5" t="str">
         <f>IF(E170="","",IF(AND(F170="نعم",G170="نعم"),"جرد + مراجعة",IF(F170="نعم","جرد فقط",IF(G170="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I170" s="9">
         <f>IF(H170="جرد + مراجعة",الإعدادات!$B$2,IF(H170="مراجعة فقط",الإعدادات!$B$3,IF(H170="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr"/>
@@ -9832,26 +9832,30 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B172" s="5" t="str">
         <f>IF(A172="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A172,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الأربعاء</v>
+        <v>الخميس</v>
       </c>
       <c r="C172" s="5" t="str">
         <f>IF(A172="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A172,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الرياض</v>
+        <v>الخرج</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9859,11 +9863,11 @@
       </c>
       <c r="H172" s="5" t="str">
         <f>IF(E172="","",IF(AND(F172="نعم",G172="نعم"),"جرد + مراجعة",IF(F172="نعم","جرد فقط",IF(G172="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I172" s="9">
         <f>IF(H172="جرد + مراجعة",الإعدادات!$B$2,IF(H172="مراجعة فقط",الإعدادات!$B$3,IF(H172="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="173">
@@ -9885,14 +9889,10 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9900,11 +9900,11 @@
       </c>
       <c r="H173" s="5" t="str">
         <f>IF(E173="","",IF(AND(F173="نعم",G173="نعم"),"جرد + مراجعة",IF(F173="نعم","جرد فقط",IF(G173="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I173" s="9">
         <f>IF(H173="جرد + مراجعة",الإعدادات!$B$2,IF(H173="مراجعة فقط",الإعدادات!$B$3,IF(H173="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174">
@@ -9922,14 +9922,18 @@
         <v>الخرج</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9937,11 +9941,11 @@
       </c>
       <c r="H174" s="5" t="str">
         <f>IF(E174="","",IF(AND(F174="نعم",G174="نعم"),"جرد + مراجعة",IF(F174="نعم","جرد فقط",IF(G174="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v>جرد + مراجعة</v>
       </c>
       <c r="I174" s="9">
         <f>IF(H174="جرد + مراجعة",الإعدادات!$B$2,IF(H174="مراجعة فقط",الإعدادات!$B$3,IF(H174="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="175">
@@ -9963,14 +9967,10 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9978,11 +9978,11 @@
       </c>
       <c r="H175" s="5" t="str">
         <f>IF(E175="","",IF(AND(F175="نعم",G175="نعم"),"جرد + مراجعة",IF(F175="نعم","جرد فقط",IF(G175="نعم","مراجعة فقط",""))))</f>
-        <v>جرد + مراجعة</v>
+        <v>مراجعة فقط</v>
       </c>
       <c r="I175" s="9">
         <f>IF(H175="جرد + مراجعة",الإعدادات!$B$2,IF(H175="مراجعة فقط",الإعدادات!$B$3,IF(H175="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr"/>
@@ -10023,40 +10023,26 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
+      <c r="A177" s="4" t="n"/>
       <c r="B177" s="5" t="str">
         <f>IF(A177="","",IFERROR(INDEX('جدول الجرد'!$A$2:$A$31,MATCH(A177,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الخميس</v>
+        <v/>
       </c>
       <c r="C177" s="5" t="str">
         <f>IF(A177="","",IFERROR(INDEX('جدول الجرد'!$E$2:$E$31,MATCH(A177,'جدول الجرد'!$B$2:$B$31,0)),""))</f>
-        <v>الخرج</v>
-      </c>
-      <c r="D177" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr"/>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="D177" s="4" t="n"/>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="n"/>
+      <c r="G177" s="4" t="n"/>
       <c r="H177" s="5" t="str">
         <f>IF(E177="","",IF(AND(F177="نعم",G177="نعم"),"جرد + مراجعة",IF(F177="نعم","جرد فقط",IF(G177="نعم","مراجعة فقط",""))))</f>
-        <v>مراجعة فقط</v>
+        <v/>
       </c>
       <c r="I177" s="9">
         <f>IF(H177="جرد + مراجعة",الإعدادات!$B$2,IF(H177="مراجعة فقط",الإعدادات!$B$3,IF(H177="جرد فقط",الإعدادات!$B$4,0)))</f>
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
